--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V669"/>
+  <dimension ref="A1:V674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64030,10 +64030,8 @@
       </c>
     </row>
     <row r="654">
-      <c r="A654" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
+      <c r="A654" t="n">
+        <v>1704</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
@@ -64085,7 +64083,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N654" s="2" t="n">
+      <c r="N654" s="1" t="n">
         <v>46156</v>
       </c>
       <c r="O654" t="inlineStr">
@@ -64126,10 +64124,8 @@
       </c>
     </row>
     <row r="655">
-      <c r="A655" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
+      <c r="A655" t="n">
+        <v>1704</v>
       </c>
       <c r="B655" t="inlineStr">
         <is>
@@ -64181,7 +64177,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N655" s="2" t="n">
+      <c r="N655" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="O655" t="inlineStr">
@@ -64222,10 +64218,8 @@
       </c>
     </row>
     <row r="656">
-      <c r="A656" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A656" t="n">
+        <v>1716</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
@@ -64277,7 +64271,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N656" s="2" t="n">
+      <c r="N656" s="1" t="n">
         <v>44153</v>
       </c>
       <c r="O656" t="inlineStr">
@@ -64318,10 +64312,8 @@
       </c>
     </row>
     <row r="657">
-      <c r="A657" t="inlineStr">
-        <is>
-          <t>1735</t>
-        </is>
+      <c r="A657" t="n">
+        <v>1735</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
@@ -64373,7 +64365,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N657" s="2" t="n">
+      <c r="N657" s="1" t="n">
         <v>44153</v>
       </c>
       <c r="O657" t="inlineStr">
@@ -64414,10 +64406,8 @@
       </c>
     </row>
     <row r="658">
-      <c r="A658" t="inlineStr">
-        <is>
-          <t>1804</t>
-        </is>
+      <c r="A658" t="n">
+        <v>1804</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
@@ -64469,7 +64459,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N658" s="2" t="n">
+      <c r="N658" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="O658" t="inlineStr">
@@ -64510,10 +64500,8 @@
       </c>
     </row>
     <row r="659">
-      <c r="A659" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A659" t="n">
+        <v>1813</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
@@ -64565,7 +64553,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N659" s="2" t="n">
+      <c r="N659" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O659" t="inlineStr">
@@ -64606,10 +64594,8 @@
       </c>
     </row>
     <row r="660">
-      <c r="A660" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A660" t="n">
+        <v>1823</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
@@ -64661,7 +64647,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N660" s="2" t="n">
+      <c r="N660" s="1" t="n">
         <v>46150</v>
       </c>
       <c r="O660" t="inlineStr">
@@ -64702,10 +64688,8 @@
       </c>
     </row>
     <row r="661">
-      <c r="A661" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A661" t="n">
+        <v>1823</v>
       </c>
       <c r="B661" t="inlineStr">
         <is>
@@ -64757,7 +64741,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N661" s="2" t="n">
+      <c r="N661" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="O661" t="inlineStr">
@@ -64798,10 +64782,8 @@
       </c>
     </row>
     <row r="662">
-      <c r="A662" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
+      <c r="A662" t="n">
+        <v>2106</v>
       </c>
       <c r="B662" t="inlineStr">
         <is>
@@ -64853,7 +64835,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N662" s="2" t="n">
+      <c r="N662" s="1" t="n">
         <v>46140</v>
       </c>
       <c r="O662" t="inlineStr">
@@ -64894,10 +64876,8 @@
       </c>
     </row>
     <row r="663">
-      <c r="A663" t="inlineStr">
-        <is>
-          <t>2738</t>
-        </is>
+      <c r="A663" t="n">
+        <v>2738</v>
       </c>
       <c r="B663" t="inlineStr">
         <is>
@@ -64949,7 +64929,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N663" s="2" t="n">
+      <c r="N663" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="O663" t="inlineStr">
@@ -64990,10 +64970,8 @@
       </c>
     </row>
     <row r="664">
-      <c r="A664" t="inlineStr">
-        <is>
-          <t>2738</t>
-        </is>
+      <c r="A664" t="n">
+        <v>2738</v>
       </c>
       <c r="B664" t="inlineStr">
         <is>
@@ -65045,7 +65023,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N664" s="2" t="n">
+      <c r="N664" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="O664" t="inlineStr">
@@ -65086,10 +65064,8 @@
       </c>
     </row>
     <row r="665">
-      <c r="A665" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
+      <c r="A665" t="n">
+        <v>2832</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
@@ -65141,7 +65117,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N665" s="2" t="n">
+      <c r="N665" s="1" t="n">
         <v>46150</v>
       </c>
       <c r="O665" t="inlineStr">
@@ -65182,10 +65158,8 @@
       </c>
     </row>
     <row r="666">
-      <c r="A666" t="inlineStr">
-        <is>
-          <t>5802</t>
-        </is>
+      <c r="A666" t="n">
+        <v>5802</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
@@ -65237,7 +65211,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N666" s="2" t="n">
+      <c r="N666" s="1" t="n">
         <v>46052</v>
       </c>
       <c r="O666" t="inlineStr">
@@ -65278,10 +65252,8 @@
       </c>
     </row>
     <row r="667">
-      <c r="A667" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A667" t="n">
+        <v>9119</v>
       </c>
       <c r="B667" t="inlineStr">
         <is>
@@ -65333,7 +65305,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N667" s="2" t="n">
+      <c r="N667" s="1" t="n">
         <v>44641</v>
       </c>
       <c r="O667" t="inlineStr">
@@ -65374,10 +65346,8 @@
       </c>
     </row>
     <row r="668">
-      <c r="A668" t="inlineStr">
-        <is>
-          <t>9131</t>
-        </is>
+      <c r="A668" t="n">
+        <v>9131</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
@@ -65429,7 +65399,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N668" s="2" t="n">
+      <c r="N668" s="1" t="n">
         <v>46147</v>
       </c>
       <c r="O668" t="inlineStr">
@@ -65470,10 +65440,8 @@
       </c>
     </row>
     <row r="669">
-      <c r="A669" t="inlineStr">
-        <is>
-          <t>9940</t>
-        </is>
+      <c r="A669" t="n">
+        <v>9940</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
@@ -65525,7 +65493,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N669" s="2" t="n">
+      <c r="N669" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="O669" t="inlineStr">
@@ -65560,6 +65528,484 @@
         </is>
       </c>
       <c r="V669" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>1125</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Leticia</t>
+        </is>
+      </c>
+      <c r="F670" t="n">
+        <v>118984</v>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>GESTIÓN TERRITORIAL INTERCULTURAL</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I670" t="n">
+        <v>135</v>
+      </c>
+      <c r="J670" t="n">
+        <v>9</v>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr"/>
+      <c r="M670" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N670" t="inlineStr"/>
+      <c r="O670" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P670" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="Q670" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="R670" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S670" t="inlineStr"/>
+      <c r="T670" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="U670" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V670" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Chía</t>
+        </is>
+      </c>
+      <c r="F671" t="n">
+        <v>118968</v>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN INTELIGENCIA ARTIFICIAL</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I671" t="n">
+        <v>162</v>
+      </c>
+      <c r="J671" t="n">
+        <v>9</v>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr"/>
+      <c r="M671" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N671" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O671" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P671" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q671" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R671" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S671" t="inlineStr"/>
+      <c r="T671" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="U671" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V671" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>4721</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA HORIZONTE</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F672" t="n">
+        <v>118967</v>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>CONTADURÍA PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I672" t="n">
+        <v>159</v>
+      </c>
+      <c r="J672" t="n">
+        <v>9</v>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr"/>
+      <c r="M672" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N672" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="O672" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P672" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q672" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R672" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S672" t="inlineStr"/>
+      <c r="T672" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="U672" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V672" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>9945</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN UNIVERSITARIA DE BOGOTA -UNIVERSITARIA DE BOGOTÁ</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F673" t="n">
+        <v>118969</v>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN CIBERSEGURIDAD Y GESTIÓN DE RIESGOS DIGITALES</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I673" t="n">
+        <v>144</v>
+      </c>
+      <c r="J673" t="n">
+        <v>9</v>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L673" t="inlineStr"/>
+      <c r="M673" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N673" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O673" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P673" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q673" t="inlineStr">
+        <is>
+          <t>Diseño y administración de redes y bases de datos</t>
+        </is>
+      </c>
+      <c r="R673" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S673" t="inlineStr"/>
+      <c r="T673" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="U673" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V673" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>9945</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN UNIVERSITARIA DE BOGOTA -UNIVERSITARIA DE BOGOTÁ</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F674" t="n">
+        <v>118970</v>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN CIBERSEGURIDAD Y GESTIÓN DE RIESGOS DIGITALES</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I674" t="n">
+        <v>144</v>
+      </c>
+      <c r="J674" t="n">
+        <v>9</v>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr"/>
+      <c r="M674" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N674" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O674" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P674" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q674" t="inlineStr">
+        <is>
+          <t>Diseño y administración de redes y bases de datos</t>
+        </is>
+      </c>
+      <c r="R674" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S674" t="inlineStr"/>
+      <c r="T674" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="U674" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V674" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -66002,10 +65999,8 @@
       </c>
     </row>
     <row r="675">
-      <c r="A675" t="inlineStr">
-        <is>
-          <t>1122</t>
-        </is>
+      <c r="A675" t="n">
+        <v>1122</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
@@ -66057,7 +66052,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N675" s="2" t="n">
+      <c r="N675" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="O675" t="inlineStr">
@@ -66098,10 +66093,8 @@
       </c>
     </row>
     <row r="676">
-      <c r="A676" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
+      <c r="A676" t="n">
+        <v>1204</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
@@ -66153,7 +66146,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N676" s="2" t="n">
+      <c r="N676" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="O676" t="inlineStr">
@@ -66194,10 +66187,8 @@
       </c>
     </row>
     <row r="677">
-      <c r="A677" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A677" t="n">
+        <v>1710</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
@@ -66249,7 +66240,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N677" s="2" t="n">
+      <c r="N677" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O677" t="inlineStr">
@@ -66290,10 +66281,8 @@
       </c>
     </row>
     <row r="678">
-      <c r="A678" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A678" t="n">
+        <v>1710</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
@@ -66345,7 +66334,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N678" s="2" t="n">
+      <c r="N678" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O678" t="inlineStr">
@@ -66386,10 +66375,8 @@
       </c>
     </row>
     <row r="679">
-      <c r="A679" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A679" t="n">
+        <v>1716</v>
       </c>
       <c r="B679" t="inlineStr">
         <is>
@@ -66441,7 +66428,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N679" s="2" t="n">
+      <c r="N679" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O679" t="inlineStr">
@@ -66482,10 +66469,8 @@
       </c>
     </row>
     <row r="680">
-      <c r="A680" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A680" t="n">
+        <v>1716</v>
       </c>
       <c r="B680" t="inlineStr">
         <is>
@@ -66537,7 +66522,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N680" s="2" t="n">
+      <c r="N680" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O680" t="inlineStr">
@@ -66578,10 +66563,8 @@
       </c>
     </row>
     <row r="681">
-      <c r="A681" t="inlineStr">
-        <is>
-          <t>1724</t>
-        </is>
+      <c r="A681" t="n">
+        <v>1724</v>
       </c>
       <c r="B681" t="inlineStr">
         <is>
@@ -66633,7 +66616,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N681" s="2" t="n">
+      <c r="N681" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="O681" t="inlineStr">
@@ -66674,10 +66657,8 @@
       </c>
     </row>
     <row r="682">
-      <c r="A682" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A682" t="n">
+        <v>1818</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
@@ -66729,7 +66710,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N682" s="2" t="n">
+      <c r="N682" s="1" t="n">
         <v>45860</v>
       </c>
       <c r="O682" t="inlineStr">
@@ -66770,10 +66751,8 @@
       </c>
     </row>
     <row r="683">
-      <c r="A683" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A683" t="n">
+        <v>1818</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
@@ -66864,10 +66843,8 @@
       </c>
     </row>
     <row r="684">
-      <c r="A684" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A684" t="n">
+        <v>2102</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
@@ -66919,7 +66896,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N684" s="2" t="n">
+      <c r="N684" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="O684" t="inlineStr">
@@ -66960,10 +66937,8 @@
       </c>
     </row>
     <row r="685">
-      <c r="A685" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A685" t="n">
+        <v>2102</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
@@ -67015,7 +66990,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N685" s="2" t="n">
+      <c r="N685" s="1" t="n">
         <v>46198</v>
       </c>
       <c r="O685" t="inlineStr">
@@ -67056,10 +67031,8 @@
       </c>
     </row>
     <row r="686">
-      <c r="A686" t="inlineStr">
-        <is>
-          <t>4835</t>
-        </is>
+      <c r="A686" t="n">
+        <v>4835</v>
       </c>
       <c r="B686" t="inlineStr">
         <is>
@@ -67111,7 +67084,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N686" s="2" t="n">
+      <c r="N686" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="O686" t="inlineStr">

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V686"/>
+  <dimension ref="A1:V687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67124,6 +67127,102 @@
         </is>
       </c>
     </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE ENVIGADO</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F687" t="n">
+        <v>119020</v>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>DERECHO</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I687" t="n">
+        <v>170</v>
+      </c>
+      <c r="J687" t="n">
+        <v>10</v>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr"/>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N687" s="2" t="n">
+        <v>45364</v>
+      </c>
+      <c r="O687" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P687" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q687" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R687" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S687" t="inlineStr"/>
+      <c r="T687" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="U687" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V687" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V687"/>
+  <dimension ref="A1:V689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67128,10 +67128,8 @@
       </c>
     </row>
     <row r="687">
-      <c r="A687" t="inlineStr">
-        <is>
-          <t>2302</t>
-        </is>
+      <c r="A687" t="n">
+        <v>2302</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
@@ -67183,7 +67181,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N687" s="2" t="n">
+      <c r="N687" s="1" t="n">
         <v>45364</v>
       </c>
       <c r="O687" t="inlineStr">
@@ -67218,6 +67216,198 @@
         </is>
       </c>
       <c r="V687" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2815</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA ADVENTISTA - UNAC</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F688" t="n">
+        <v>119025</v>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>CONTADURIA PUBLICA</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I688" t="n">
+        <v>153</v>
+      </c>
+      <c r="J688" t="n">
+        <v>9</v>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr"/>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N688" s="2" t="n">
+        <v>43817</v>
+      </c>
+      <c r="O688" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P688" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q688" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R688" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S688" t="inlineStr"/>
+      <c r="T688" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="U688" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V688" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA - ITM</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F689" t="n">
+        <v>119023</v>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>DISEÑO</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I689" t="n">
+        <v>130</v>
+      </c>
+      <c r="J689" t="n">
+        <v>8</v>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr"/>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N689" s="2" t="n">
+        <v>44392</v>
+      </c>
+      <c r="O689" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P689" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q689" t="inlineStr">
+        <is>
+          <t>Diseño industrial, de moda e interiores</t>
+        </is>
+      </c>
+      <c r="R689" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S689" t="inlineStr"/>
+      <c r="T689" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="U689" t="inlineStr">
+        <is>
+          <t>Escuela de Arquitectura, Urbanismo y Diseño</t>
+        </is>
+      </c>
+      <c r="V689" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V689"/>
+  <dimension ref="A1:V707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67222,10 +67222,8 @@
       </c>
     </row>
     <row r="688">
-      <c r="A688" t="inlineStr">
-        <is>
-          <t>2815</t>
-        </is>
+      <c r="A688" t="n">
+        <v>2815</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
@@ -67277,7 +67275,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N688" s="2" t="n">
+      <c r="N688" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O688" t="inlineStr">
@@ -67318,10 +67316,8 @@
       </c>
     </row>
     <row r="689">
-      <c r="A689" t="inlineStr">
-        <is>
-          <t>3302</t>
-        </is>
+      <c r="A689" t="n">
+        <v>3302</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
@@ -67373,7 +67369,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N689" s="2" t="n">
+      <c r="N689" s="1" t="n">
         <v>44392</v>
       </c>
       <c r="O689" t="inlineStr">
@@ -67408,6 +67404,1734 @@
         </is>
       </c>
       <c r="V689" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CALDAS</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>La Dorada</t>
+        </is>
+      </c>
+      <c r="F690" t="n">
+        <v>119015</v>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN AGROINDUSTRIA Y TECNOLOGÍAS INTELIGENTES</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I690" t="n">
+        <v>144</v>
+      </c>
+      <c r="J690" t="n">
+        <v>8</v>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr"/>
+      <c r="M690" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N690" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="O690" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P690" t="inlineStr">
+        <is>
+          <t>Industria y procesamiento</t>
+        </is>
+      </c>
+      <c r="Q690" t="inlineStr">
+        <is>
+          <t>Procesamiento de alimentos</t>
+        </is>
+      </c>
+      <c r="R690" t="inlineStr">
+        <is>
+          <t>Ingeniería agroindustrial, alimentos y afines</t>
+        </is>
+      </c>
+      <c r="S690" t="inlineStr"/>
+      <c r="T690" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U690" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V690" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SURCOLOMBIANA</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>Pitalito</t>
+        </is>
+      </c>
+      <c r="F691" t="n">
+        <v>119051</v>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DEL CAFÉ</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I691" t="n">
+        <v>157</v>
+      </c>
+      <c r="J691" t="n">
+        <v>10</v>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr"/>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N691" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O691" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P691" t="inlineStr">
+        <is>
+          <t>Industria y procesamiento</t>
+        </is>
+      </c>
+      <c r="Q691" t="inlineStr">
+        <is>
+          <t>Procesamiento de alimentos</t>
+        </is>
+      </c>
+      <c r="R691" t="inlineStr">
+        <is>
+          <t>Ingeniería agroindustrial, alimentos y afines</t>
+        </is>
+      </c>
+      <c r="S691" t="inlineStr"/>
+      <c r="T691" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U691" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V691" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>1213</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL MAGDALENA - UNIMAGDALENA</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>Santa Marta</t>
+        </is>
+      </c>
+      <c r="F692" t="n">
+        <v>119041</v>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>GENÉTICA</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I692" t="n">
+        <v>145</v>
+      </c>
+      <c r="J692" t="n">
+        <v>9</v>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr"/>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N692" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="O692" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P692" t="inlineStr">
+        <is>
+          <t>Ciencias biológicas y afines</t>
+        </is>
+      </c>
+      <c r="Q692" t="inlineStr">
+        <is>
+          <t>Ciencias biológicas y afines no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R692" t="inlineStr">
+        <is>
+          <t>Biología, microbiología y afines</t>
+        </is>
+      </c>
+      <c r="S692" t="inlineStr"/>
+      <c r="T692" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U692" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="V692" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F693" t="n">
+        <v>119031</v>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>COMUNICACIÓN SOCIAL</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I693" t="n">
+        <v>126</v>
+      </c>
+      <c r="J693" t="n">
+        <v>8</v>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr"/>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N693" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O693" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P693" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q693" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R693" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S693" t="inlineStr"/>
+      <c r="T693" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U693" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V693" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA UNAD</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F694" t="n">
+        <v>119034</v>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN INTELIGENCIA ARTIFICIAL Y CIENCIA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I694" t="n">
+        <v>150</v>
+      </c>
+      <c r="J694" t="n">
+        <v>9</v>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L694" t="inlineStr"/>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N694" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O694" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P694" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q694" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R694" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S694" t="inlineStr"/>
+      <c r="T694" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U694" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V694" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2715</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DE POPAYAN</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>Popayán</t>
+        </is>
+      </c>
+      <c r="F695" t="n">
+        <v>119068</v>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>COMUNICACIÓN SOCIAL</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I695" t="n">
+        <v>138</v>
+      </c>
+      <c r="J695" t="n">
+        <v>8</v>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr"/>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N695" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O695" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P695" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q695" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R695" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S695" t="inlineStr"/>
+      <c r="T695" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U695" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V695" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2725</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>POLITECNICO GRANCOLOMBIANO</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F696" t="n">
+        <v>119028</v>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>GOBIERNO Y RELACIONES INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I696" t="n">
+        <v>143</v>
+      </c>
+      <c r="J696" t="n">
+        <v>8</v>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr"/>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N696" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O696" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P696" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q696" t="inlineStr">
+        <is>
+          <t>Ciencias políticas y educación cívica</t>
+        </is>
+      </c>
+      <c r="R696" t="inlineStr">
+        <is>
+          <t>Ciencia política, relaciones internacionales</t>
+        </is>
+      </c>
+      <c r="S696" t="inlineStr"/>
+      <c r="T696" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U696" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V696" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2828</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DEL HUILA-CORHUILA-</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F697" t="n">
+        <v>118734</v>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I697" t="n">
+        <v>144</v>
+      </c>
+      <c r="J697" t="n">
+        <v>8</v>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr"/>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N697" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="O697" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P697" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q697" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R697" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S697" t="inlineStr"/>
+      <c r="T697" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U697" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V697" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2828</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DEL HUILA-CORHUILA-</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F698" t="n">
+        <v>118733</v>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I698" t="n">
+        <v>144</v>
+      </c>
+      <c r="J698" t="n">
+        <v>8</v>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr"/>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N698" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="O698" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P698" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q698" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R698" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S698" t="inlineStr"/>
+      <c r="T698" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U698" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V698" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>3115</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA DEL PUTUMAYO</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Mocoa</t>
+        </is>
+      </c>
+      <c r="F699" t="n">
+        <v>118941</v>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>INGENIERÍA AGROPECUARIA</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I699" t="n">
+        <v>180</v>
+      </c>
+      <c r="J699" t="n">
+        <v>10</v>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr"/>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N699" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O699" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P699" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q699" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R699" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S699" t="inlineStr"/>
+      <c r="T699" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U699" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V699" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>3115</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA DEL PUTUMAYO</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Mocoa</t>
+        </is>
+      </c>
+      <c r="F700" t="n">
+        <v>118939</v>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I700" t="n">
+        <v>161</v>
+      </c>
+      <c r="J700" t="n">
+        <v>10</v>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr"/>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N700" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O700" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P700" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q700" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R700" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S700" t="inlineStr"/>
+      <c r="T700" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U700" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V700" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>4817</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>CORPORACION DE EDUCACIÓN SUPERIOR DEL LITORAL</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F701" t="n">
+        <v>119075</v>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I701" t="n">
+        <v>144</v>
+      </c>
+      <c r="J701" t="n">
+        <v>8</v>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr"/>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N701" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O701" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P701" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q701" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R701" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S701" t="inlineStr"/>
+      <c r="T701" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U701" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V701" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>4817</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>CORPORACION DE EDUCACIÓN SUPERIOR DEL LITORAL</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F702" t="n">
+        <v>119076</v>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I702" t="n">
+        <v>144</v>
+      </c>
+      <c r="J702" t="n">
+        <v>8</v>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr"/>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N702" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O702" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P702" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q702" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R702" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S702" t="inlineStr"/>
+      <c r="T702" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U702" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V702" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F703" t="n">
+        <v>119027</v>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>CONTADURÍA PUBLICA</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I703" t="n">
+        <v>140</v>
+      </c>
+      <c r="J703" t="n">
+        <v>8</v>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr"/>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N703" s="2" t="n">
+        <v>45796</v>
+      </c>
+      <c r="O703" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P703" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q703" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R703" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S703" t="inlineStr"/>
+      <c r="T703" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U703" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V703" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F704" t="n">
+        <v>119026</v>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>CONTADURÍA PUBLICA</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I704" t="n">
+        <v>140</v>
+      </c>
+      <c r="J704" t="n">
+        <v>8</v>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr"/>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N704" s="2" t="n">
+        <v>45796</v>
+      </c>
+      <c r="O704" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P704" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q704" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R704" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S704" t="inlineStr"/>
+      <c r="T704" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U704" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V704" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>9906</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN UNIVERSITARIA PARA EL DESARROLLO EMPRESARIAL Y SOCIAL - MISIÓN PAZ.</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F705" t="n">
+        <v>119084</v>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I705" t="n">
+        <v>144</v>
+      </c>
+      <c r="J705" t="n">
+        <v>8</v>
+      </c>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr"/>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N705" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="O705" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P705" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="Q705" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="R705" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S705" t="inlineStr"/>
+      <c r="T705" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U705" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V705" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>9906</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN UNIVERSITARIA PARA EL DESARROLLO EMPRESARIAL Y SOCIAL - MISIÓN PAZ.</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F706" t="n">
+        <v>119083</v>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>COMUNICACIÓN SOCIAL</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I706" t="n">
+        <v>144</v>
+      </c>
+      <c r="J706" t="n">
+        <v>8</v>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr"/>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N706" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="O706" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P706" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q706" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R706" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S706" t="inlineStr"/>
+      <c r="T706" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U706" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V706" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>9939</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>FUNDACIÓN UNIVERSITARIA CATÓLICA DEL CARIBE</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F707" t="n">
+        <v>119029</v>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN EN SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I707" t="n">
+        <v>143</v>
+      </c>
+      <c r="J707" t="n">
+        <v>9</v>
+      </c>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L707" t="inlineStr"/>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N707" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O707" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P707" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q707" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R707" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S707" t="inlineStr"/>
+      <c r="T707" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U707" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V707" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V707"/>
+  <dimension ref="A1:V722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67410,10 +67410,8 @@
       </c>
     </row>
     <row r="690">
-      <c r="A690" t="inlineStr">
-        <is>
-          <t>1112</t>
-        </is>
+      <c r="A690" t="n">
+        <v>1112</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
@@ -67465,7 +67463,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N690" s="2" t="n">
+      <c r="N690" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="O690" t="inlineStr">
@@ -67506,10 +67504,8 @@
       </c>
     </row>
     <row r="691">
-      <c r="A691" t="inlineStr">
-        <is>
-          <t>1114</t>
-        </is>
+      <c r="A691" t="n">
+        <v>1114</v>
       </c>
       <c r="B691" t="inlineStr">
         <is>
@@ -67561,7 +67557,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N691" s="2" t="n">
+      <c r="N691" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O691" t="inlineStr">
@@ -67602,10 +67598,8 @@
       </c>
     </row>
     <row r="692">
-      <c r="A692" t="inlineStr">
-        <is>
-          <t>1213</t>
-        </is>
+      <c r="A692" t="n">
+        <v>1213</v>
       </c>
       <c r="B692" t="inlineStr">
         <is>
@@ -67657,7 +67651,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N692" s="2" t="n">
+      <c r="N692" s="1" t="n">
         <v>46197</v>
       </c>
       <c r="O692" t="inlineStr">
@@ -67698,10 +67692,8 @@
       </c>
     </row>
     <row r="693">
-      <c r="A693" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A693" t="n">
+        <v>1722</v>
       </c>
       <c r="B693" t="inlineStr">
         <is>
@@ -67753,7 +67745,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N693" s="2" t="n">
+      <c r="N693" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O693" t="inlineStr">
@@ -67794,10 +67786,8 @@
       </c>
     </row>
     <row r="694">
-      <c r="A694" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A694" t="n">
+        <v>2102</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
@@ -67849,7 +67839,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N694" s="2" t="n">
+      <c r="N694" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O694" t="inlineStr">
@@ -67890,10 +67880,8 @@
       </c>
     </row>
     <row r="695">
-      <c r="A695" t="inlineStr">
-        <is>
-          <t>2715</t>
-        </is>
+      <c r="A695" t="n">
+        <v>2715</v>
       </c>
       <c r="B695" t="inlineStr">
         <is>
@@ -67945,7 +67933,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N695" s="2" t="n">
+      <c r="N695" s="1" t="n">
         <v>46125</v>
       </c>
       <c r="O695" t="inlineStr">
@@ -67986,10 +67974,8 @@
       </c>
     </row>
     <row r="696">
-      <c r="A696" t="inlineStr">
-        <is>
-          <t>2725</t>
-        </is>
+      <c r="A696" t="n">
+        <v>2725</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
@@ -68041,7 +68027,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N696" s="2" t="n">
+      <c r="N696" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O696" t="inlineStr">
@@ -68082,10 +68068,8 @@
       </c>
     </row>
     <row r="697">
-      <c r="A697" t="inlineStr">
-        <is>
-          <t>2828</t>
-        </is>
+      <c r="A697" t="n">
+        <v>2828</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
@@ -68137,7 +68121,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N697" s="2" t="n">
+      <c r="N697" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="O697" t="inlineStr">
@@ -68178,10 +68162,8 @@
       </c>
     </row>
     <row r="698">
-      <c r="A698" t="inlineStr">
-        <is>
-          <t>2828</t>
-        </is>
+      <c r="A698" t="n">
+        <v>2828</v>
       </c>
       <c r="B698" t="inlineStr">
         <is>
@@ -68233,7 +68215,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N698" s="2" t="n">
+      <c r="N698" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="O698" t="inlineStr">
@@ -68274,10 +68256,8 @@
       </c>
     </row>
     <row r="699">
-      <c r="A699" t="inlineStr">
-        <is>
-          <t>3115</t>
-        </is>
+      <c r="A699" t="n">
+        <v>3115</v>
       </c>
       <c r="B699" t="inlineStr">
         <is>
@@ -68329,7 +68309,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N699" s="2" t="n">
+      <c r="N699" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O699" t="inlineStr">
@@ -68370,10 +68350,8 @@
       </c>
     </row>
     <row r="700">
-      <c r="A700" t="inlineStr">
-        <is>
-          <t>3115</t>
-        </is>
+      <c r="A700" t="n">
+        <v>3115</v>
       </c>
       <c r="B700" t="inlineStr">
         <is>
@@ -68425,7 +68403,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N700" s="2" t="n">
+      <c r="N700" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O700" t="inlineStr">
@@ -68466,10 +68444,8 @@
       </c>
     </row>
     <row r="701">
-      <c r="A701" t="inlineStr">
-        <is>
-          <t>4817</t>
-        </is>
+      <c r="A701" t="n">
+        <v>4817</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
@@ -68521,7 +68497,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N701" s="2" t="n">
+      <c r="N701" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="O701" t="inlineStr">
@@ -68562,10 +68538,8 @@
       </c>
     </row>
     <row r="702">
-      <c r="A702" t="inlineStr">
-        <is>
-          <t>4817</t>
-        </is>
+      <c r="A702" t="n">
+        <v>4817</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
@@ -68617,7 +68591,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N702" s="2" t="n">
+      <c r="N702" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="O702" t="inlineStr">
@@ -68658,10 +68632,8 @@
       </c>
     </row>
     <row r="703">
-      <c r="A703" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A703" t="n">
+        <v>9119</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
@@ -68713,7 +68685,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N703" s="2" t="n">
+      <c r="N703" s="1" t="n">
         <v>45796</v>
       </c>
       <c r="O703" t="inlineStr">
@@ -68754,10 +68726,8 @@
       </c>
     </row>
     <row r="704">
-      <c r="A704" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A704" t="n">
+        <v>9119</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
@@ -68809,7 +68779,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N704" s="2" t="n">
+      <c r="N704" s="1" t="n">
         <v>45796</v>
       </c>
       <c r="O704" t="inlineStr">
@@ -68850,10 +68820,8 @@
       </c>
     </row>
     <row r="705">
-      <c r="A705" t="inlineStr">
-        <is>
-          <t>9906</t>
-        </is>
+      <c r="A705" t="n">
+        <v>9906</v>
       </c>
       <c r="B705" t="inlineStr">
         <is>
@@ -68905,7 +68873,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N705" s="2" t="n">
+      <c r="N705" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="O705" t="inlineStr">
@@ -68946,10 +68914,8 @@
       </c>
     </row>
     <row r="706">
-      <c r="A706" t="inlineStr">
-        <is>
-          <t>9906</t>
-        </is>
+      <c r="A706" t="n">
+        <v>9906</v>
       </c>
       <c r="B706" t="inlineStr">
         <is>
@@ -69001,7 +68967,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N706" s="2" t="n">
+      <c r="N706" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="O706" t="inlineStr">
@@ -69042,10 +69008,8 @@
       </c>
     </row>
     <row r="707">
-      <c r="A707" t="inlineStr">
-        <is>
-          <t>9939</t>
-        </is>
+      <c r="A707" t="n">
+        <v>9939</v>
       </c>
       <c r="B707" t="inlineStr">
         <is>
@@ -69097,7 +69061,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N707" s="2" t="n">
+      <c r="N707" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O707" t="inlineStr">
@@ -69132,6 +69096,1422 @@
         </is>
       </c>
       <c r="V707" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CALDAS</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F708" t="n">
+        <v>119154</v>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>ECONOMÍA</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I708" t="n">
+        <v>141</v>
+      </c>
+      <c r="J708" t="n">
+        <v>8</v>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L708" t="inlineStr"/>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N708" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O708" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P708" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q708" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R708" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S708" t="inlineStr"/>
+      <c r="T708" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="U708" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V708" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL TOLIMA</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr"/>
+      <c r="E709" t="inlineStr"/>
+      <c r="F709" t="n">
+        <v>119127</v>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN EVALUACIÓN Y GESTIÓN DE POLÍTICAS PÚBLICAS PARA LA IGUALDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I709" t="n">
+        <v>23</v>
+      </c>
+      <c r="J709" t="n">
+        <v>2</v>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L709" t="inlineStr"/>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N709" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="O709" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P709" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q709" t="inlineStr">
+        <is>
+          <t>Ciencias políticas y educación cívica</t>
+        </is>
+      </c>
+      <c r="R709" t="inlineStr">
+        <is>
+          <t>Ciencia política, relaciones internacionales</t>
+        </is>
+      </c>
+      <c r="S709" t="inlineStr"/>
+      <c r="T709" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="U709" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V709" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>1732</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F710" t="n">
+        <v>119171</v>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I710" t="n">
+        <v>136</v>
+      </c>
+      <c r="J710" t="n">
+        <v>8</v>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L710" t="inlineStr"/>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N710" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O710" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P710" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q710" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R710" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S710" t="inlineStr"/>
+      <c r="T710" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="U710" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V710" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2209</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>POLITECNICO COLOMBIANO JAIME ISAZA CADAVID</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F711" t="n">
+        <v>119169</v>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>MEDICINA VETERINARIA  Y ZOOTECNIA</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I711" t="n">
+        <v>175</v>
+      </c>
+      <c r="J711" t="n">
+        <v>10</v>
+      </c>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L711" t="inlineStr"/>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N711" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O711" t="inlineStr">
+        <is>
+          <t>Agropecuario, Silvicultura, Pesca y Veterinaria</t>
+        </is>
+      </c>
+      <c r="P711" t="inlineStr">
+        <is>
+          <t>Veterinaria</t>
+        </is>
+      </c>
+      <c r="Q711" t="inlineStr">
+        <is>
+          <t>Veterinaria</t>
+        </is>
+      </c>
+      <c r="R711" t="inlineStr">
+        <is>
+          <t>Medicina veterinaria</t>
+        </is>
+      </c>
+      <c r="S711" t="inlineStr"/>
+      <c r="T711" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="U711" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V711" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>UNIDAD CENTRAL DEL VALLE DEL CAUCA</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>Tuluá</t>
+        </is>
+      </c>
+      <c r="F712" t="n">
+        <v>119129</v>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN ENERGÍAS</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I712" t="n">
+        <v>156</v>
+      </c>
+      <c r="J712" t="n">
+        <v>10</v>
+      </c>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L712" t="inlineStr"/>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N712" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O712" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P712" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q712" t="inlineStr">
+        <is>
+          <t>Electricidad y energía</t>
+        </is>
+      </c>
+      <c r="R712" t="inlineStr">
+        <is>
+          <t>Ingeniería eléctrica y afines</t>
+        </is>
+      </c>
+      <c r="S712" t="inlineStr"/>
+      <c r="T712" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="U712" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V712" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE ENVIGADO</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F713" t="n">
+        <v>119149</v>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>CIENCIA POLÍTICA Y GESTIÓN PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I713" t="n">
+        <v>151</v>
+      </c>
+      <c r="J713" t="n">
+        <v>9</v>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L713" t="inlineStr"/>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N713" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="O713" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P713" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q713" t="inlineStr">
+        <is>
+          <t>Ciencias políticas y educación cívica</t>
+        </is>
+      </c>
+      <c r="R713" t="inlineStr">
+        <is>
+          <t>Ciencia política, relaciones internacionales</t>
+        </is>
+      </c>
+      <c r="S713" t="inlineStr"/>
+      <c r="T713" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="U713" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V713" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2749</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA  SALAZAR Y HERRERA</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F714" t="n">
+        <v>119161</v>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>INGENIERIA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I714" t="n">
+        <v>163</v>
+      </c>
+      <c r="J714" t="n">
+        <v>10</v>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L714" t="inlineStr"/>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N714" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O714" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P714" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q714" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R714" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S714" t="inlineStr"/>
+      <c r="T714" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="U714" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V714" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2813</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EIA</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F715" t="n">
+        <v>119142</v>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>DISEÑO</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I715" t="n">
+        <v>140</v>
+      </c>
+      <c r="J715" t="n">
+        <v>8</v>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr"/>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N715" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="O715" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P715" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q715" t="inlineStr">
+        <is>
+          <t>Diseño industrial, de moda e interiores</t>
+        </is>
+      </c>
+      <c r="R715" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S715" t="inlineStr"/>
+      <c r="T715" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="U715" t="inlineStr">
+        <is>
+          <t>Escuela de Arquitectura, Urbanismo y Diseño</t>
+        </is>
+      </c>
+      <c r="V715" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2827</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DEL META - UNIMETA</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>Puerto López</t>
+        </is>
+      </c>
+      <c r="F716" t="n">
+        <v>119141</v>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>INGENIERIA AGROINDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I716" t="n">
+        <v>164</v>
+      </c>
+      <c r="J716" t="n">
+        <v>10</v>
+      </c>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr"/>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N716" s="2" t="n">
+        <v>44530</v>
+      </c>
+      <c r="O716" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P716" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q716" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R716" t="inlineStr">
+        <is>
+          <t>Ingeniería agroindustrial, alimentos y afines</t>
+        </is>
+      </c>
+      <c r="S716" t="inlineStr"/>
+      <c r="T716" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="U716" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V716" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>UNIDADES TECNOLOGICAS DE SANTANDER</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr"/>
+      <c r="E717" t="inlineStr"/>
+      <c r="F717" t="n">
+        <v>119126</v>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>INGENIERÍA AGROINDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I717" t="n">
+        <v>152</v>
+      </c>
+      <c r="J717" t="n">
+        <v>10</v>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr"/>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N717" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="O717" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P717" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q717" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R717" t="inlineStr">
+        <is>
+          <t>Ingeniería agroindustrial, alimentos y afines</t>
+        </is>
+      </c>
+      <c r="S717" t="inlineStr"/>
+      <c r="T717" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="U717" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V717" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>4107</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA TÉCNICA PARA EL DESARROLLO PROFESIONAL - UTEDÉ</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>Guadalajara de Buga</t>
+        </is>
+      </c>
+      <c r="F718" t="n">
+        <v>119140</v>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>PROFESIONAL UNIVERSITARIO EN LOGÍSTICA INTEGRAL</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I718" t="n">
+        <v>154</v>
+      </c>
+      <c r="J718" t="n">
+        <v>3</v>
+      </c>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr"/>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N718" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O718" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P718" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="Q718" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="R718" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S718" t="inlineStr"/>
+      <c r="T718" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="U718" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V718" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F719" t="n">
+        <v>119137</v>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>DISEÑO GRÁFICO</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I719" t="n">
+        <v>154</v>
+      </c>
+      <c r="J719" t="n">
+        <v>9</v>
+      </c>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr"/>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N719" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O719" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P719" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q719" t="inlineStr">
+        <is>
+          <t>Técnicas audiovisuales y producción para medios de comunicación</t>
+        </is>
+      </c>
+      <c r="R719" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S719" t="inlineStr"/>
+      <c r="T719" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="U719" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="V719" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr"/>
+      <c r="E720" t="inlineStr"/>
+      <c r="F720" t="n">
+        <v>119125</v>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I720" t="n">
+        <v>144</v>
+      </c>
+      <c r="J720" t="n">
+        <v>8</v>
+      </c>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L720" t="inlineStr"/>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N720" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O720" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P720" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q720" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R720" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S720" t="inlineStr"/>
+      <c r="T720" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="U720" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V720" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>9922</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA COMFAMILIAR RISARALDA</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="F721" t="n">
+        <v>119150</v>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN CIENCIA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I721" t="n">
+        <v>141</v>
+      </c>
+      <c r="J721" t="n">
+        <v>8</v>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr"/>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N721" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="O721" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P721" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q721" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R721" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S721" t="inlineStr"/>
+      <c r="T721" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="U721" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V721" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>9927</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DIGITAL DE ANTIOQUIA -IU. DIGITAL</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F722" t="n">
+        <v>119128</v>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>DERECHO</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I722" t="n">
+        <v>165</v>
+      </c>
+      <c r="J722" t="n">
+        <v>10</v>
+      </c>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L722" t="inlineStr"/>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N722" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="O722" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P722" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q722" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R722" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S722" t="inlineStr"/>
+      <c r="T722" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="U722" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V722" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V722"/>
+  <dimension ref="A1:V757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69102,10 +69102,8 @@
       </c>
     </row>
     <row r="708">
-      <c r="A708" t="inlineStr">
-        <is>
-          <t>1112</t>
-        </is>
+      <c r="A708" t="n">
+        <v>1112</v>
       </c>
       <c r="B708" t="inlineStr">
         <is>
@@ -69157,7 +69155,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N708" s="2" t="n">
+      <c r="N708" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O708" t="inlineStr">
@@ -69198,10 +69196,8 @@
       </c>
     </row>
     <row r="709">
-      <c r="A709" t="inlineStr">
-        <is>
-          <t>1207</t>
-        </is>
+      <c r="A709" t="n">
+        <v>1207</v>
       </c>
       <c r="B709" t="inlineStr">
         <is>
@@ -69245,7 +69241,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N709" s="2" t="n">
+      <c r="N709" s="1" t="n">
         <v>46148</v>
       </c>
       <c r="O709" t="inlineStr">
@@ -69286,10 +69282,8 @@
       </c>
     </row>
     <row r="710">
-      <c r="A710" t="inlineStr">
-        <is>
-          <t>1732</t>
-        </is>
+      <c r="A710" t="n">
+        <v>1732</v>
       </c>
       <c r="B710" t="inlineStr">
         <is>
@@ -69341,7 +69335,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N710" s="2" t="n">
+      <c r="N710" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O710" t="inlineStr">
@@ -69382,10 +69376,8 @@
       </c>
     </row>
     <row r="711">
-      <c r="A711" t="inlineStr">
-        <is>
-          <t>2209</t>
-        </is>
+      <c r="A711" t="n">
+        <v>2209</v>
       </c>
       <c r="B711" t="inlineStr">
         <is>
@@ -69437,7 +69429,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N711" s="2" t="n">
+      <c r="N711" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O711" t="inlineStr">
@@ -69478,10 +69470,8 @@
       </c>
     </row>
     <row r="712">
-      <c r="A712" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
+      <c r="A712" t="n">
+        <v>2301</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
@@ -69533,7 +69523,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N712" s="2" t="n">
+      <c r="N712" s="1" t="n">
         <v>46154</v>
       </c>
       <c r="O712" t="inlineStr">
@@ -69574,10 +69564,8 @@
       </c>
     </row>
     <row r="713">
-      <c r="A713" t="inlineStr">
-        <is>
-          <t>2302</t>
-        </is>
+      <c r="A713" t="n">
+        <v>2302</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
@@ -69629,7 +69617,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N713" s="2" t="n">
+      <c r="N713" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="O713" t="inlineStr">
@@ -69670,10 +69658,8 @@
       </c>
     </row>
     <row r="714">
-      <c r="A714" t="inlineStr">
-        <is>
-          <t>2749</t>
-        </is>
+      <c r="A714" t="n">
+        <v>2749</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
@@ -69725,7 +69711,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N714" s="2" t="n">
+      <c r="N714" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O714" t="inlineStr">
@@ -69766,10 +69752,8 @@
       </c>
     </row>
     <row r="715">
-      <c r="A715" t="inlineStr">
-        <is>
-          <t>2813</t>
-        </is>
+      <c r="A715" t="n">
+        <v>2813</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
@@ -69821,7 +69805,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N715" s="2" t="n">
+      <c r="N715" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="O715" t="inlineStr">
@@ -69862,10 +69846,8 @@
       </c>
     </row>
     <row r="716">
-      <c r="A716" t="inlineStr">
-        <is>
-          <t>2827</t>
-        </is>
+      <c r="A716" t="n">
+        <v>2827</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
@@ -69917,7 +69899,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N716" s="2" t="n">
+      <c r="N716" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="O716" t="inlineStr">
@@ -69958,10 +69940,8 @@
       </c>
     </row>
     <row r="717">
-      <c r="A717" t="inlineStr">
-        <is>
-          <t>3201</t>
-        </is>
+      <c r="A717" t="n">
+        <v>3201</v>
       </c>
       <c r="B717" t="inlineStr">
         <is>
@@ -70005,7 +69985,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N717" s="2" t="n">
+      <c r="N717" s="1" t="n">
         <v>46148</v>
       </c>
       <c r="O717" t="inlineStr">
@@ -70046,10 +70026,8 @@
       </c>
     </row>
     <row r="718">
-      <c r="A718" t="inlineStr">
-        <is>
-          <t>4107</t>
-        </is>
+      <c r="A718" t="n">
+        <v>4107</v>
       </c>
       <c r="B718" t="inlineStr">
         <is>
@@ -70101,7 +70079,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N718" s="2" t="n">
+      <c r="N718" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="O718" t="inlineStr">
@@ -70142,10 +70120,8 @@
       </c>
     </row>
     <row r="719">
-      <c r="A719" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A719" t="n">
+        <v>4813</v>
       </c>
       <c r="B719" t="inlineStr">
         <is>
@@ -70197,7 +70173,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N719" s="2" t="n">
+      <c r="N719" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O719" t="inlineStr">
@@ -70238,10 +70214,8 @@
       </c>
     </row>
     <row r="720">
-      <c r="A720" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A720" t="n">
+        <v>9119</v>
       </c>
       <c r="B720" t="inlineStr">
         <is>
@@ -70285,7 +70259,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N720" s="2" t="n">
+      <c r="N720" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O720" t="inlineStr">
@@ -70326,10 +70300,8 @@
       </c>
     </row>
     <row r="721">
-      <c r="A721" t="inlineStr">
-        <is>
-          <t>9922</t>
-        </is>
+      <c r="A721" t="n">
+        <v>9922</v>
       </c>
       <c r="B721" t="inlineStr">
         <is>
@@ -70381,7 +70353,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N721" s="2" t="n">
+      <c r="N721" s="1" t="n">
         <v>46147</v>
       </c>
       <c r="O721" t="inlineStr">
@@ -70422,10 +70394,8 @@
       </c>
     </row>
     <row r="722">
-      <c r="A722" t="inlineStr">
-        <is>
-          <t>9927</t>
-        </is>
+      <c r="A722" t="n">
+        <v>9927</v>
       </c>
       <c r="B722" t="inlineStr">
         <is>
@@ -70477,7 +70447,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N722" s="2" t="n">
+      <c r="N722" s="1" t="n">
         <v>46149</v>
       </c>
       <c r="O722" t="inlineStr">
@@ -70512,6 +70482,3366 @@
         </is>
       </c>
       <c r="V722" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL QUINDIO</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="F723" t="n">
+        <v>119294</v>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>INGENIERÍA FORESTAL</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I723" t="n">
+        <v>157</v>
+      </c>
+      <c r="J723" t="n">
+        <v>10</v>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr"/>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N723" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="O723" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P723" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q723" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R723" t="inlineStr">
+        <is>
+          <t>Ingeniería agrícola, forestal y afines</t>
+        </is>
+      </c>
+      <c r="S723" t="inlineStr"/>
+      <c r="T723" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U723" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V723" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE PAMPLONA</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>Pamplona</t>
+        </is>
+      </c>
+      <c r="F724" t="n">
+        <v>119194</v>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>ZOOTECNIA</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I724" t="n">
+        <v>148</v>
+      </c>
+      <c r="J724" t="n">
+        <v>9</v>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr"/>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N724" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="O724" t="inlineStr">
+        <is>
+          <t>Agropecuario, Silvicultura, Pesca y Veterinaria</t>
+        </is>
+      </c>
+      <c r="P724" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="Q724" t="inlineStr">
+        <is>
+          <t>Producción agrícola y ganadera</t>
+        </is>
+      </c>
+      <c r="R724" t="inlineStr">
+        <is>
+          <t>Zootecnia</t>
+        </is>
+      </c>
+      <c r="S724" t="inlineStr"/>
+      <c r="T724" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U724" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V724" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CUNDINAMARCA</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>Soacha</t>
+        </is>
+      </c>
+      <c r="F725" t="n">
+        <v>119184</v>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN ROBÓTICA Y AUTOMATIZACIÓN</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I725" t="n">
+        <v>150</v>
+      </c>
+      <c r="J725" t="n">
+        <v>9</v>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L725" t="inlineStr"/>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N725" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O725" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P725" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q725" t="inlineStr">
+        <is>
+          <t>Electrónica y automatización</t>
+        </is>
+      </c>
+      <c r="R725" t="inlineStr">
+        <is>
+          <t>Ingeniería electrónica, telecomunicaciones y afines</t>
+        </is>
+      </c>
+      <c r="S725" t="inlineStr"/>
+      <c r="T725" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U725" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V725" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F726" t="n">
+        <v>119172</v>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>CIENCIA POLÍTICA</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I726" t="n">
+        <v>132</v>
+      </c>
+      <c r="J726" t="n">
+        <v>8</v>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L726" t="inlineStr"/>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N726" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O726" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P726" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q726" t="inlineStr">
+        <is>
+          <t>Ciencias políticas y educación cívica</t>
+        </is>
+      </c>
+      <c r="R726" t="inlineStr">
+        <is>
+          <t>Ciencia política, relaciones internacionales</t>
+        </is>
+      </c>
+      <c r="S726" t="inlineStr"/>
+      <c r="T726" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U726" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V726" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PONTIFICIA BOLIVARIANA</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F727" t="n">
+        <v>119186</v>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>COMUNICACIÓN Y NARRATIVAS DIGITALES</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I727" t="n">
+        <v>120</v>
+      </c>
+      <c r="J727" t="n">
+        <v>8</v>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L727" t="inlineStr"/>
+      <c r="M727" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N727" s="2" t="n">
+        <v>45365</v>
+      </c>
+      <c r="O727" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P727" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q727" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R727" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S727" t="inlineStr"/>
+      <c r="T727" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U727" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V727" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>1732</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F728" t="n">
+        <v>119237</v>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I728" t="n">
+        <v>129</v>
+      </c>
+      <c r="J728" t="n">
+        <v>8</v>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr"/>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N728" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O728" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P728" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q728" t="inlineStr">
+        <is>
+          <t>Electrónica y automatización</t>
+        </is>
+      </c>
+      <c r="R728" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S728" t="inlineStr"/>
+      <c r="T728" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U728" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V728" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>1732</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F729" t="n">
+        <v>119193</v>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>NUTRICIÓN Y DIETÉTICA</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I729" t="n">
+        <v>159</v>
+      </c>
+      <c r="J729" t="n">
+        <v>9</v>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr"/>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N729" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="O729" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P729" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q729" t="inlineStr">
+        <is>
+          <t>Salud no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R729" t="inlineStr">
+        <is>
+          <t>Nutrición y dietética</t>
+        </is>
+      </c>
+      <c r="S729" t="inlineStr"/>
+      <c r="T729" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U729" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V729" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MEDELLIN</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F730" t="n">
+        <v>119197</v>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>DISEÑO Y GESTIÓN ARTESANAL</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I730" t="n">
+        <v>138</v>
+      </c>
+      <c r="J730" t="n">
+        <v>8</v>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr"/>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N730" s="2" t="n">
+        <v>45104</v>
+      </c>
+      <c r="O730" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P730" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q730" t="inlineStr">
+        <is>
+          <t>Diseño industrial, de moda e interiores</t>
+        </is>
+      </c>
+      <c r="R730" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S730" t="inlineStr"/>
+      <c r="T730" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U730" t="inlineStr">
+        <is>
+          <t>Escuela de Arquitectura, Urbanismo y Diseño</t>
+        </is>
+      </c>
+      <c r="V730" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>1817</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="F731" t="n">
+        <v>119289</v>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>INGENIERÍA AGROALIMENTARIA</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I731" t="n">
+        <v>155</v>
+      </c>
+      <c r="J731" t="n">
+        <v>9</v>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr"/>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N731" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="O731" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P731" t="inlineStr">
+        <is>
+          <t>Ciencias físicas</t>
+        </is>
+      </c>
+      <c r="Q731" t="inlineStr">
+        <is>
+          <t>Ciencias de la tierra</t>
+        </is>
+      </c>
+      <c r="R731" t="inlineStr">
+        <is>
+          <t>Ingeniería agroindustrial, alimentos y afines</t>
+        </is>
+      </c>
+      <c r="S731" t="inlineStr"/>
+      <c r="T731" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U731" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="V731" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F732" t="n">
+        <v>119195</v>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>ASUNTOS GLOBALES Y RELACIONES INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I732" t="n">
+        <v>136</v>
+      </c>
+      <c r="J732" t="n">
+        <v>8</v>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr"/>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N732" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="O732" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P732" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q732" t="inlineStr">
+        <is>
+          <t>Ciencias políticas y educación cívica</t>
+        </is>
+      </c>
+      <c r="R732" t="inlineStr">
+        <is>
+          <t>Ciencia política, relaciones internacionales</t>
+        </is>
+      </c>
+      <c r="S732" t="inlineStr"/>
+      <c r="T732" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U732" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V732" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2723</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA AGRARIA DE COLOMBIA -UNIAGRARIA-</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F733" t="n">
+        <v>119267</v>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>PROFESIONAL EN CIENCIA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I733" t="n">
+        <v>132</v>
+      </c>
+      <c r="J733" t="n">
+        <v>8</v>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L733" t="inlineStr"/>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N733" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="O733" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P733" t="inlineStr">
+        <is>
+          <t>Matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q733" t="inlineStr">
+        <is>
+          <t>Estadística</t>
+        </is>
+      </c>
+      <c r="R733" t="inlineStr">
+        <is>
+          <t>Matemáticas, estadística y afines</t>
+        </is>
+      </c>
+      <c r="S733" t="inlineStr"/>
+      <c r="T733" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U733" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="V733" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2743</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD INTERNACIONAL DEL TRÓPICO AMERICANO - UNITRÓPICO</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>Yopal</t>
+        </is>
+      </c>
+      <c r="F734" t="n">
+        <v>119288</v>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN INTELIGENCIA ARTIFICIAL</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I734" t="n">
+        <v>148</v>
+      </c>
+      <c r="J734" t="n">
+        <v>9</v>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr"/>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N734" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="O734" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P734" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q734" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R734" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S734" t="inlineStr"/>
+      <c r="T734" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U734" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V734" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2744</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CESMAG - UNICESMAG</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="F735" t="n">
+        <v>119230</v>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>FISIOTERAPIA</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I735" t="n">
+        <v>159</v>
+      </c>
+      <c r="J735" t="n">
+        <v>9</v>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr"/>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N735" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="O735" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P735" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q735" t="inlineStr">
+        <is>
+          <t>Fisioterapia, Fonoaudiología, Terapia ocupacional, Nutrición y afines</t>
+        </is>
+      </c>
+      <c r="R735" t="inlineStr">
+        <is>
+          <t>Instrumentación quirúrgica</t>
+        </is>
+      </c>
+      <c r="S735" t="inlineStr"/>
+      <c r="T735" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U735" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V735" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F736" t="n">
+        <v>119239</v>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>DERECHO</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I736" t="n">
+        <v>160</v>
+      </c>
+      <c r="J736" t="n">
+        <v>9</v>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr"/>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N736" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="O736" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P736" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q736" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R736" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S736" t="inlineStr"/>
+      <c r="T736" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U736" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V736" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F737" t="n">
+        <v>119238</v>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>DERECHO</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I737" t="n">
+        <v>160</v>
+      </c>
+      <c r="J737" t="n">
+        <v>9</v>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr"/>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N737" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="O737" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P737" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q737" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R737" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S737" t="inlineStr"/>
+      <c r="T737" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U737" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V737" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>TECNOLÓGICO DE ARTES DÉBORA ARANGO INSTITUCIÓN REDEFINIDA</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F738" t="n">
+        <v>119226</v>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>PROFESIONAL UNIVERSITARIO EN DISEÑO GRÁFICO</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I738" t="n">
+        <v>136</v>
+      </c>
+      <c r="J738" t="n">
+        <v>8</v>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr"/>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N738" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="O738" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P738" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q738" t="inlineStr">
+        <is>
+          <t>Artes no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R738" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S738" t="inlineStr"/>
+      <c r="T738" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U738" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V738" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>3705</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA TECNOLOGICO COMFENALCO - CARTAGENA</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F739" t="n">
+        <v>119236</v>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>INGENIERIA QUIMICA</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I739" t="n">
+        <v>170</v>
+      </c>
+      <c r="J739" t="n">
+        <v>10</v>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr"/>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N739" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O739" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P739" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q739" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R739" t="inlineStr">
+        <is>
+          <t>Ingeniería química y afines</t>
+        </is>
+      </c>
+      <c r="S739" t="inlineStr"/>
+      <c r="T739" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U739" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V739" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>4719</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>FUNDACION DE EDUCACION SUPERIOR NUEVA AMERICA</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F740" t="n">
+        <v>119243</v>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>PROFESIONAL UNIVERSITARIO EN MARKETING  Y PUBLICIDAD</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I740" t="n">
+        <v>133</v>
+      </c>
+      <c r="J740" t="n">
+        <v>8</v>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr"/>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N740" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="O740" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P740" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q740" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R740" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S740" t="inlineStr"/>
+      <c r="T740" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U740" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V740" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>4719</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>FUNDACION DE EDUCACION SUPERIOR NUEVA AMERICA</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F741" t="n">
+        <v>119242</v>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>PROFESIONAL UNIVERSITARIO EN MARKETING  Y PUBLICIDAD</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I741" t="n">
+        <v>133</v>
+      </c>
+      <c r="J741" t="n">
+        <v>8</v>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr"/>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N741" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="O741" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P741" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q741" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R741" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S741" t="inlineStr"/>
+      <c r="T741" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U741" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V741" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F742" t="n">
+        <v>119286</v>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE LA SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I742" t="n">
+        <v>154</v>
+      </c>
+      <c r="J742" t="n">
+        <v>9</v>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr"/>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N742" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O742" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P742" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q742" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R742" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S742" t="inlineStr"/>
+      <c r="T742" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U742" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V742" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F743" t="n">
+        <v>119285</v>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE LA SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I743" t="n">
+        <v>154</v>
+      </c>
+      <c r="J743" t="n">
+        <v>9</v>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr"/>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N743" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O743" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P743" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q743" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R743" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S743" t="inlineStr"/>
+      <c r="T743" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U743" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V743" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F744" t="n">
+        <v>119178</v>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>DISEÑO DE EXPERIENCIAS INTERACTIVAS</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I744" t="n">
+        <v>158</v>
+      </c>
+      <c r="J744" t="n">
+        <v>9</v>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr"/>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N744" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O744" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P744" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q744" t="inlineStr">
+        <is>
+          <t>Técnicas audiovisuales y producción para medios de comunicación</t>
+        </is>
+      </c>
+      <c r="R744" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S744" t="inlineStr"/>
+      <c r="T744" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U744" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="V744" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F745" t="n">
+        <v>119179</v>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>DISEÑO DE EXPERIENCIAS INTERACTIVAS</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I745" t="n">
+        <v>158</v>
+      </c>
+      <c r="J745" t="n">
+        <v>9</v>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr"/>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N745" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O745" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P745" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q745" t="inlineStr">
+        <is>
+          <t>Técnicas audiovisuales y producción para medios de comunicación</t>
+        </is>
+      </c>
+      <c r="R745" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S745" t="inlineStr"/>
+      <c r="T745" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U745" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="V745" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="F746" t="n">
+        <v>119176</v>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I746" t="n">
+        <v>156</v>
+      </c>
+      <c r="J746" t="n">
+        <v>9</v>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr"/>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N746" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="O746" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P746" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q746" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R746" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S746" t="inlineStr"/>
+      <c r="T746" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U746" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V746" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F747" t="n">
+        <v>119177</v>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I747" t="n">
+        <v>156</v>
+      </c>
+      <c r="J747" t="n">
+        <v>9</v>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr"/>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N747" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="O747" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P747" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q747" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R747" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S747" t="inlineStr"/>
+      <c r="T747" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U747" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V747" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="F748" t="n">
+        <v>119261</v>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>MARKETING DIGITAL</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I748" t="n">
+        <v>159</v>
+      </c>
+      <c r="J748" t="n">
+        <v>9</v>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr"/>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N748" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O748" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P748" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q748" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R748" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S748" t="inlineStr"/>
+      <c r="T748" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U748" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V748" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F749" t="n">
+        <v>119262</v>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>MARKETING DIGITAL</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I749" t="n">
+        <v>159</v>
+      </c>
+      <c r="J749" t="n">
+        <v>9</v>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr"/>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N749" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O749" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P749" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q749" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R749" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S749" t="inlineStr"/>
+      <c r="T749" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U749" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V749" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>4817</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>CORPORACION DE EDUCACIÓN SUPERIOR DEL LITORAL</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F750" t="n">
+        <v>119292</v>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>MARKETING Y NEGOCIOS DIGITALES</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I750" t="n">
+        <v>146</v>
+      </c>
+      <c r="J750" t="n">
+        <v>8</v>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr"/>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N750" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="O750" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P750" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q750" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R750" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S750" t="inlineStr"/>
+      <c r="T750" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U750" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V750" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>4817</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>CORPORACION DE EDUCACIÓN SUPERIOR DEL LITORAL</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F751" t="n">
+        <v>119293</v>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>MARKETING Y NEGOCIOS DIGITALES</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I751" t="n">
+        <v>146</v>
+      </c>
+      <c r="J751" t="n">
+        <v>8</v>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr"/>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N751" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="O751" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P751" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q751" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R751" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S751" t="inlineStr"/>
+      <c r="T751" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U751" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V751" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="F752" t="n">
+        <v>119182</v>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN EDUCACIÓN INFANTIL</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I752" t="n">
+        <v>144</v>
+      </c>
+      <c r="J752" t="n">
+        <v>8</v>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr"/>
+      <c r="M752" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N752" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O752" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P752" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q752" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R752" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S752" t="inlineStr"/>
+      <c r="T752" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U752" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V752" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F753" t="n">
+        <v>119214</v>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN LENGUAS EXTRANJERAS  CON ÉNFASIS EN INGLÉS</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I753" t="n">
+        <v>168</v>
+      </c>
+      <c r="J753" t="n">
+        <v>10</v>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L753" t="inlineStr"/>
+      <c r="M753" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N753" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="O753" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P753" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q753" t="inlineStr">
+        <is>
+          <t>Formación para docentes con asignatura de especialización</t>
+        </is>
+      </c>
+      <c r="R753" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S753" t="inlineStr"/>
+      <c r="T753" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U753" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V753" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F754" t="n">
+        <v>119213</v>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN LENGUAS EXTRANJERAS  CON ÉNFASIS EN INGLÉS</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I754" t="n">
+        <v>168</v>
+      </c>
+      <c r="J754" t="n">
+        <v>10</v>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L754" t="inlineStr"/>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N754" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="O754" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P754" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q754" t="inlineStr">
+        <is>
+          <t>Formación para docentes con asignatura de especialización</t>
+        </is>
+      </c>
+      <c r="R754" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S754" t="inlineStr"/>
+      <c r="T754" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U754" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V754" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>9899</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE COLOMBIA - UNIVERSITARIA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F755" t="n">
+        <v>119271</v>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>CONTADURÍA PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I755" t="n">
+        <v>144</v>
+      </c>
+      <c r="J755" t="n">
+        <v>9</v>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L755" t="inlineStr"/>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N755" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="O755" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P755" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q755" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R755" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S755" t="inlineStr"/>
+      <c r="T755" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U755" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V755" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>9927</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DIGITAL DE ANTIOQUIA -IU. DIGITAL</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F756" t="n">
+        <v>119077</v>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>COMUNICACIÓN Y PERIODISMO DIGITAL</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I756" t="n">
+        <v>147</v>
+      </c>
+      <c r="J756" t="n">
+        <v>9</v>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L756" t="inlineStr"/>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N756" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O756" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P756" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q756" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R756" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S756" t="inlineStr"/>
+      <c r="T756" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U756" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V756" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>9946</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA PÚBLICA DE BELLO - IUPBELLO</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="F757" t="n">
+        <v>119273</v>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I757" t="n">
+        <v>144</v>
+      </c>
+      <c r="J757" t="n">
+        <v>8</v>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr"/>
+      <c r="M757" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N757" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="O757" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P757" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q757" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R757" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S757" t="inlineStr"/>
+      <c r="T757" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="U757" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V757" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V757"/>
+  <dimension ref="A1:V783"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70488,10 +70488,8 @@
       </c>
     </row>
     <row r="723">
-      <c r="A723" t="inlineStr">
-        <is>
-          <t>1208</t>
-        </is>
+      <c r="A723" t="n">
+        <v>1208</v>
       </c>
       <c r="B723" t="inlineStr">
         <is>
@@ -70543,7 +70541,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N723" s="2" t="n">
+      <c r="N723" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="O723" t="inlineStr">
@@ -70584,10 +70582,8 @@
       </c>
     </row>
     <row r="724">
-      <c r="A724" t="inlineStr">
-        <is>
-          <t>1212</t>
-        </is>
+      <c r="A724" t="n">
+        <v>1212</v>
       </c>
       <c r="B724" t="inlineStr">
         <is>
@@ -70639,7 +70635,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N724" s="2" t="n">
+      <c r="N724" s="1" t="n">
         <v>46218</v>
       </c>
       <c r="O724" t="inlineStr">
@@ -70680,10 +70676,8 @@
       </c>
     </row>
     <row r="725">
-      <c r="A725" t="inlineStr">
-        <is>
-          <t>1214</t>
-        </is>
+      <c r="A725" t="n">
+        <v>1214</v>
       </c>
       <c r="B725" t="inlineStr">
         <is>
@@ -70735,7 +70729,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N725" s="2" t="n">
+      <c r="N725" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O725" t="inlineStr">
@@ -70776,10 +70770,8 @@
       </c>
     </row>
     <row r="726">
-      <c r="A726" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A726" t="n">
+        <v>1722</v>
       </c>
       <c r="B726" t="inlineStr">
         <is>
@@ -70831,7 +70823,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N726" s="2" t="n">
+      <c r="N726" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O726" t="inlineStr">
@@ -70872,10 +70864,8 @@
       </c>
     </row>
     <row r="727">
-      <c r="A727" t="inlineStr">
-        <is>
-          <t>1723</t>
-        </is>
+      <c r="A727" t="n">
+        <v>1723</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
@@ -70927,7 +70917,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N727" s="2" t="n">
+      <c r="N727" s="1" t="n">
         <v>45365</v>
       </c>
       <c r="O727" t="inlineStr">
@@ -70968,10 +70958,8 @@
       </c>
     </row>
     <row r="728">
-      <c r="A728" t="inlineStr">
-        <is>
-          <t>1732</t>
-        </is>
+      <c r="A728" t="n">
+        <v>1732</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
@@ -71023,7 +71011,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N728" s="2" t="n">
+      <c r="N728" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="O728" t="inlineStr">
@@ -71064,10 +71052,8 @@
       </c>
     </row>
     <row r="729">
-      <c r="A729" t="inlineStr">
-        <is>
-          <t>1732</t>
-        </is>
+      <c r="A729" t="n">
+        <v>1732</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
@@ -71119,7 +71105,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N729" s="2" t="n">
+      <c r="N729" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="O729" t="inlineStr">
@@ -71160,10 +71146,8 @@
       </c>
     </row>
     <row r="730">
-      <c r="A730" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A730" t="n">
+        <v>1812</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
@@ -71215,7 +71199,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N730" s="2" t="n">
+      <c r="N730" s="1" t="n">
         <v>45104</v>
       </c>
       <c r="O730" t="inlineStr">
@@ -71256,10 +71240,8 @@
       </c>
     </row>
     <row r="731">
-      <c r="A731" t="inlineStr">
-        <is>
-          <t>1817</t>
-        </is>
+      <c r="A731" t="n">
+        <v>1817</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
@@ -71311,7 +71293,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N731" s="2" t="n">
+      <c r="N731" s="1" t="n">
         <v>46210</v>
       </c>
       <c r="O731" t="inlineStr">
@@ -71352,10 +71334,8 @@
       </c>
     </row>
     <row r="732">
-      <c r="A732" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A732" t="n">
+        <v>1828</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
@@ -71407,7 +71387,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N732" s="2" t="n">
+      <c r="N732" s="1" t="n">
         <v>46218</v>
       </c>
       <c r="O732" t="inlineStr">
@@ -71448,10 +71428,8 @@
       </c>
     </row>
     <row r="733">
-      <c r="A733" t="inlineStr">
-        <is>
-          <t>2723</t>
-        </is>
+      <c r="A733" t="n">
+        <v>2723</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
@@ -71503,7 +71481,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N733" s="2" t="n">
+      <c r="N733" s="1" t="n">
         <v>46218</v>
       </c>
       <c r="O733" t="inlineStr">
@@ -71544,10 +71522,8 @@
       </c>
     </row>
     <row r="734">
-      <c r="A734" t="inlineStr">
-        <is>
-          <t>2743</t>
-        </is>
+      <c r="A734" t="n">
+        <v>2743</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
@@ -71599,7 +71575,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N734" s="2" t="n">
+      <c r="N734" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="O734" t="inlineStr">
@@ -71640,10 +71616,8 @@
       </c>
     </row>
     <row r="735">
-      <c r="A735" t="inlineStr">
-        <is>
-          <t>2744</t>
-        </is>
+      <c r="A735" t="n">
+        <v>2744</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
@@ -71695,7 +71669,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N735" s="2" t="n">
+      <c r="N735" s="1" t="n">
         <v>46205</v>
       </c>
       <c r="O735" t="inlineStr">
@@ -71736,10 +71710,8 @@
       </c>
     </row>
     <row r="736">
-      <c r="A736" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A736" t="n">
+        <v>2829</v>
       </c>
       <c r="B736" t="inlineStr">
         <is>
@@ -71791,7 +71763,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N736" s="2" t="n">
+      <c r="N736" s="1" t="n">
         <v>46155</v>
       </c>
       <c r="O736" t="inlineStr">
@@ -71832,10 +71804,8 @@
       </c>
     </row>
     <row r="737">
-      <c r="A737" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A737" t="n">
+        <v>2829</v>
       </c>
       <c r="B737" t="inlineStr">
         <is>
@@ -71887,7 +71857,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N737" s="2" t="n">
+      <c r="N737" s="1" t="n">
         <v>46155</v>
       </c>
       <c r="O737" t="inlineStr">
@@ -71928,10 +71898,8 @@
       </c>
     </row>
     <row r="738">
-      <c r="A738" t="inlineStr">
-        <is>
-          <t>3303</t>
-        </is>
+      <c r="A738" t="n">
+        <v>3303</v>
       </c>
       <c r="B738" t="inlineStr">
         <is>
@@ -71983,7 +71951,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N738" s="2" t="n">
+      <c r="N738" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="O738" t="inlineStr">
@@ -72024,10 +71992,8 @@
       </c>
     </row>
     <row r="739">
-      <c r="A739" t="inlineStr">
-        <is>
-          <t>3705</t>
-        </is>
+      <c r="A739" t="n">
+        <v>3705</v>
       </c>
       <c r="B739" t="inlineStr">
         <is>
@@ -72079,7 +72045,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N739" s="2" t="n">
+      <c r="N739" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="O739" t="inlineStr">
@@ -72120,10 +72086,8 @@
       </c>
     </row>
     <row r="740">
-      <c r="A740" t="inlineStr">
-        <is>
-          <t>4719</t>
-        </is>
+      <c r="A740" t="n">
+        <v>4719</v>
       </c>
       <c r="B740" t="inlineStr">
         <is>
@@ -72175,7 +72139,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N740" s="2" t="n">
+      <c r="N740" s="1" t="n">
         <v>46147</v>
       </c>
       <c r="O740" t="inlineStr">
@@ -72216,10 +72180,8 @@
       </c>
     </row>
     <row r="741">
-      <c r="A741" t="inlineStr">
-        <is>
-          <t>4719</t>
-        </is>
+      <c r="A741" t="n">
+        <v>4719</v>
       </c>
       <c r="B741" t="inlineStr">
         <is>
@@ -72271,7 +72233,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N741" s="2" t="n">
+      <c r="N741" s="1" t="n">
         <v>46147</v>
       </c>
       <c r="O741" t="inlineStr">
@@ -72312,10 +72274,8 @@
       </c>
     </row>
     <row r="742">
-      <c r="A742" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A742" t="n">
+        <v>4813</v>
       </c>
       <c r="B742" t="inlineStr">
         <is>
@@ -72367,7 +72327,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N742" s="2" t="n">
+      <c r="N742" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O742" t="inlineStr">
@@ -72408,10 +72368,8 @@
       </c>
     </row>
     <row r="743">
-      <c r="A743" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A743" t="n">
+        <v>4813</v>
       </c>
       <c r="B743" t="inlineStr">
         <is>
@@ -72463,7 +72421,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N743" s="2" t="n">
+      <c r="N743" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O743" t="inlineStr">
@@ -72504,10 +72462,8 @@
       </c>
     </row>
     <row r="744">
-      <c r="A744" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A744" t="n">
+        <v>4813</v>
       </c>
       <c r="B744" t="inlineStr">
         <is>
@@ -72559,7 +72515,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N744" s="2" t="n">
+      <c r="N744" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O744" t="inlineStr">
@@ -72600,10 +72556,8 @@
       </c>
     </row>
     <row r="745">
-      <c r="A745" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A745" t="n">
+        <v>4813</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
@@ -72655,7 +72609,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N745" s="2" t="n">
+      <c r="N745" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O745" t="inlineStr">
@@ -72696,10 +72650,8 @@
       </c>
     </row>
     <row r="746">
-      <c r="A746" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A746" t="n">
+        <v>4813</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
@@ -72751,7 +72703,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N746" s="2" t="n">
+      <c r="N746" s="1" t="n">
         <v>46126</v>
       </c>
       <c r="O746" t="inlineStr">
@@ -72792,10 +72744,8 @@
       </c>
     </row>
     <row r="747">
-      <c r="A747" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A747" t="n">
+        <v>4813</v>
       </c>
       <c r="B747" t="inlineStr">
         <is>
@@ -72847,7 +72797,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N747" s="2" t="n">
+      <c r="N747" s="1" t="n">
         <v>46126</v>
       </c>
       <c r="O747" t="inlineStr">
@@ -72888,10 +72838,8 @@
       </c>
     </row>
     <row r="748">
-      <c r="A748" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A748" t="n">
+        <v>4813</v>
       </c>
       <c r="B748" t="inlineStr">
         <is>
@@ -72943,7 +72891,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N748" s="2" t="n">
+      <c r="N748" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O748" t="inlineStr">
@@ -72984,10 +72932,8 @@
       </c>
     </row>
     <row r="749">
-      <c r="A749" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A749" t="n">
+        <v>4813</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
@@ -73039,7 +72985,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N749" s="2" t="n">
+      <c r="N749" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O749" t="inlineStr">
@@ -73080,10 +73026,8 @@
       </c>
     </row>
     <row r="750">
-      <c r="A750" t="inlineStr">
-        <is>
-          <t>4817</t>
-        </is>
+      <c r="A750" t="n">
+        <v>4817</v>
       </c>
       <c r="B750" t="inlineStr">
         <is>
@@ -73135,7 +73079,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N750" s="2" t="n">
+      <c r="N750" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="O750" t="inlineStr">
@@ -73176,10 +73120,8 @@
       </c>
     </row>
     <row r="751">
-      <c r="A751" t="inlineStr">
-        <is>
-          <t>4817</t>
-        </is>
+      <c r="A751" t="n">
+        <v>4817</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
@@ -73231,7 +73173,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N751" s="2" t="n">
+      <c r="N751" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="O751" t="inlineStr">
@@ -73272,10 +73214,8 @@
       </c>
     </row>
     <row r="752">
-      <c r="A752" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A752" t="n">
+        <v>9119</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
@@ -73327,7 +73267,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N752" s="2" t="n">
+      <c r="N752" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O752" t="inlineStr">
@@ -73368,10 +73308,8 @@
       </c>
     </row>
     <row r="753">
-      <c r="A753" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A753" t="n">
+        <v>9119</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
@@ -73423,7 +73361,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N753" s="2" t="n">
+      <c r="N753" s="1" t="n">
         <v>46015</v>
       </c>
       <c r="O753" t="inlineStr">
@@ -73464,10 +73402,8 @@
       </c>
     </row>
     <row r="754">
-      <c r="A754" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A754" t="n">
+        <v>9119</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
@@ -73519,7 +73455,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N754" s="2" t="n">
+      <c r="N754" s="1" t="n">
         <v>46015</v>
       </c>
       <c r="O754" t="inlineStr">
@@ -73560,10 +73496,8 @@
       </c>
     </row>
     <row r="755">
-      <c r="A755" t="inlineStr">
-        <is>
-          <t>9899</t>
-        </is>
+      <c r="A755" t="n">
+        <v>9899</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
@@ -73615,7 +73549,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N755" s="2" t="n">
+      <c r="N755" s="1" t="n">
         <v>46218</v>
       </c>
       <c r="O755" t="inlineStr">
@@ -73656,10 +73590,8 @@
       </c>
     </row>
     <row r="756">
-      <c r="A756" t="inlineStr">
-        <is>
-          <t>9927</t>
-        </is>
+      <c r="A756" t="n">
+        <v>9927</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
@@ -73711,7 +73643,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N756" s="2" t="n">
+      <c r="N756" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O756" t="inlineStr">
@@ -73752,10 +73684,8 @@
       </c>
     </row>
     <row r="757">
-      <c r="A757" t="inlineStr">
-        <is>
-          <t>9946</t>
-        </is>
+      <c r="A757" t="n">
+        <v>9946</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
@@ -73807,7 +73737,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N757" s="2" t="n">
+      <c r="N757" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="O757" t="inlineStr">
@@ -73842,6 +73772,2502 @@
         </is>
       </c>
       <c r="V757" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL TOLIMA</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="F758" t="n">
+        <v>119314</v>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>INGENIERÍA CIVIL</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I758" t="n">
+        <v>162</v>
+      </c>
+      <c r="J758" t="n">
+        <v>9</v>
+      </c>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L758" t="inlineStr"/>
+      <c r="M758" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N758" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="O758" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P758" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q758" t="inlineStr">
+        <is>
+          <t>Construcción e ingeniería civil</t>
+        </is>
+      </c>
+      <c r="R758" t="inlineStr">
+        <is>
+          <t>Ingeniería civil y afines</t>
+        </is>
+      </c>
+      <c r="S758" t="inlineStr"/>
+      <c r="T758" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U758" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V758" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CENTRAL</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F759" t="n">
+        <v>115829</v>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>ECONOMÍA Y FINANZAS</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I759" t="n">
+        <v>141</v>
+      </c>
+      <c r="J759" t="n">
+        <v>8</v>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L759" t="inlineStr"/>
+      <c r="M759" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N759" s="2" t="n">
+        <v>45906</v>
+      </c>
+      <c r="O759" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P759" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q759" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R759" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S759" t="inlineStr"/>
+      <c r="T759" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U759" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V759" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F760" t="n">
+        <v>119328</v>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>INGENIERÍA FORESTAL Y DEL MEDIO NATURAL</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I760" t="n">
+        <v>150</v>
+      </c>
+      <c r="J760" t="n">
+        <v>9</v>
+      </c>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L760" t="inlineStr"/>
+      <c r="M760" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N760" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="O760" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P760" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q760" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R760" t="inlineStr">
+        <is>
+          <t>Ingeniería agrícola, forestal y afines</t>
+        </is>
+      </c>
+      <c r="S760" t="inlineStr"/>
+      <c r="T760" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U760" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V760" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTIAGO DE CALI</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F761" t="n">
+        <v>119324</v>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN DESARROLLO DE VIDEOJUEGOS</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I761" t="n">
+        <v>147</v>
+      </c>
+      <c r="J761" t="n">
+        <v>9</v>
+      </c>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L761" t="inlineStr"/>
+      <c r="M761" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N761" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="O761" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P761" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q761" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R761" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S761" t="inlineStr"/>
+      <c r="T761" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U761" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V761" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ANTONIO NARIÑO</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F762" t="n">
+        <v>119381</v>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>INGENIERÍA BIOMÉDICA</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I762" t="n">
+        <v>143</v>
+      </c>
+      <c r="J762" t="n">
+        <v>8</v>
+      </c>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L762" t="inlineStr"/>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N762" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O762" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P762" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q762" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R762" t="inlineStr">
+        <is>
+          <t>Ingeniería biomédica y afines</t>
+        </is>
+      </c>
+      <c r="S762" t="inlineStr"/>
+      <c r="T762" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U762" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V762" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ANTONIO NARIÑO</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>Popayán</t>
+        </is>
+      </c>
+      <c r="F763" t="n">
+        <v>119330</v>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>MEDICINA</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I763" t="n">
+        <v>276</v>
+      </c>
+      <c r="J763" t="n">
+        <v>12</v>
+      </c>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L763" t="inlineStr"/>
+      <c r="M763" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N763" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="O763" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P763" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q763" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R763" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S763" t="inlineStr"/>
+      <c r="T763" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U763" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V763" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ANTONIO NARIÑO</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F764" t="n">
+        <v>119383</v>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>OPTOMETRÍA</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I764" t="n">
+        <v>166</v>
+      </c>
+      <c r="J764" t="n">
+        <v>9</v>
+      </c>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L764" t="inlineStr"/>
+      <c r="M764" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N764" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O764" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P764" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q764" t="inlineStr">
+        <is>
+          <t>Salud no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R764" t="inlineStr">
+        <is>
+          <t>Optometría, otros programas de ciencias de la salud</t>
+        </is>
+      </c>
+      <c r="S764" t="inlineStr"/>
+      <c r="T764" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U764" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V764" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2110</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>COLEGIO MAYOR DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F765" t="n">
+        <v>119307</v>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>PROFESIONAL EN SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I765" t="n">
+        <v>135</v>
+      </c>
+      <c r="J765" t="n">
+        <v>8</v>
+      </c>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L765" t="inlineStr"/>
+      <c r="M765" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N765" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="O765" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="P765" t="inlineStr">
+        <is>
+          <t>Servicios de higiene y salud ocupacional</t>
+        </is>
+      </c>
+      <c r="Q765" t="inlineStr">
+        <is>
+          <t>Salud y protección laboral</t>
+        </is>
+      </c>
+      <c r="R765" t="inlineStr">
+        <is>
+          <t>Salud pública</t>
+        </is>
+      </c>
+      <c r="S765" t="inlineStr"/>
+      <c r="T765" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U765" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V765" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2746</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA SANITAS</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F766" t="n">
+        <v>119329</v>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>QUÍMICA FARMACÉUTICA</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I766" t="n">
+        <v>181</v>
+      </c>
+      <c r="J766" t="n">
+        <v>10</v>
+      </c>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L766" t="inlineStr"/>
+      <c r="M766" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N766" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="O766" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P766" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q766" t="inlineStr">
+        <is>
+          <t>Salud no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R766" t="inlineStr">
+        <is>
+          <t>Química y afines</t>
+        </is>
+      </c>
+      <c r="S766" t="inlineStr"/>
+      <c r="T766" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U766" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V766" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F767" t="n">
+        <v>119390</v>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I767" t="n">
+        <v>144</v>
+      </c>
+      <c r="J767" t="n">
+        <v>9</v>
+      </c>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L767" t="inlineStr"/>
+      <c r="M767" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N767" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O767" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P767" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q767" t="inlineStr">
+        <is>
+          <t>Electrónica y automatización</t>
+        </is>
+      </c>
+      <c r="R767" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S767" t="inlineStr"/>
+      <c r="T767" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U767" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V767" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2837</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REPUBLICANA</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F768" t="n">
+        <v>119370</v>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>DERECHO</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I768" t="n">
+        <v>165</v>
+      </c>
+      <c r="J768" t="n">
+        <v>10</v>
+      </c>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L768" t="inlineStr"/>
+      <c r="M768" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N768" s="2" t="n">
+        <v>44589</v>
+      </c>
+      <c r="O768" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P768" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q768" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R768" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S768" t="inlineStr"/>
+      <c r="T768" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U768" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V768" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>3117</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA DE BARRANQUILLA - IUB</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F769" t="n">
+        <v>119310</v>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>BIOTECNOLOGÍA</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I769" t="n">
+        <v>163</v>
+      </c>
+      <c r="J769" t="n">
+        <v>13</v>
+      </c>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L769" t="inlineStr"/>
+      <c r="M769" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N769" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="O769" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P769" t="inlineStr">
+        <is>
+          <t>Ciencias biológicas y afines</t>
+        </is>
+      </c>
+      <c r="Q769" t="inlineStr">
+        <is>
+          <t>Ciencias biológicas y afines no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R769" t="inlineStr">
+        <is>
+          <t>Biología, microbiología y afines</t>
+        </is>
+      </c>
+      <c r="S769" t="inlineStr"/>
+      <c r="T769" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U769" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="V769" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>UNIDADES TECNOLOGICAS DE SANTANDER</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F770" t="n">
+        <v>119351</v>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I770" t="n">
+        <v>154</v>
+      </c>
+      <c r="J770" t="n">
+        <v>10</v>
+      </c>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L770" t="inlineStr"/>
+      <c r="M770" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N770" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="O770" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P770" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q770" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R770" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S770" t="inlineStr"/>
+      <c r="T770" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U770" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V770" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>TECNOLÓGICO DE ARTES DÉBORA ARANGO INSTITUCIÓN REDEFINIDA</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F771" t="n">
+        <v>119317</v>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>PROFESIONAL UNIVERSITARIO EN DESARROLLO DE EXPERIENCIAS PARA LA INTERACCIÓN DIGITAL</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I771" t="n">
+        <v>106</v>
+      </c>
+      <c r="J771" t="n">
+        <v>8</v>
+      </c>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L771" t="inlineStr"/>
+      <c r="M771" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N771" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O771" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P771" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q771" t="inlineStr">
+        <is>
+          <t>Artes no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R771" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S771" t="inlineStr"/>
+      <c r="T771" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U771" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V771" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>3821</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA POLITECNICO COSTA ATLANTICA</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F772" t="n">
+        <v>119306</v>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>DERECHO</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I772" t="n">
+        <v>154</v>
+      </c>
+      <c r="J772" t="n">
+        <v>9</v>
+      </c>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L772" t="inlineStr"/>
+      <c r="M772" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N772" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="O772" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P772" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q772" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R772" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S772" t="inlineStr"/>
+      <c r="T772" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U772" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V772" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE FORMACION TECNICA PROFESIONAL DE SAN JUAN DEL CESAR</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>San Juan del Cesar</t>
+        </is>
+      </c>
+      <c r="F773" t="n">
+        <v>119378</v>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>PROGRAMA ADMINISTRACIÓN DE EMPRESA ARTICULADO POR CICLOS PROPEDÉUTICOS CON LOS PROGRAMAS TECNOLOGÍA EN GESTIÓN EMPRESARIAL Y TÉCNICA PROFESIONAL EN PROCESOS ADMINISTRATIVOS</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I773" t="n">
+        <v>147</v>
+      </c>
+      <c r="J773" t="n">
+        <v>9</v>
+      </c>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L773" t="inlineStr"/>
+      <c r="M773" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N773" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="O773" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P773" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q773" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R773" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S773" t="inlineStr"/>
+      <c r="T773" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U773" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V773" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA DEL CARIBE</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>Aracataca</t>
+        </is>
+      </c>
+      <c r="F774" t="n">
+        <v>119368</v>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>ADMINISTRACION DE AGRONEGOCIOS</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I774" t="n">
+        <v>159</v>
+      </c>
+      <c r="J774" t="n">
+        <v>10</v>
+      </c>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L774" t="inlineStr"/>
+      <c r="M774" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N774" s="2" t="n">
+        <v>45104</v>
+      </c>
+      <c r="O774" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P774" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q774" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R774" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S774" t="inlineStr"/>
+      <c r="T774" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U774" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V774" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA DEL CARIBE</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>Aracataca</t>
+        </is>
+      </c>
+      <c r="F775" t="n">
+        <v>119364</v>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>CONTADURIA PUBLICA</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I775" t="n">
+        <v>163</v>
+      </c>
+      <c r="J775" t="n">
+        <v>10</v>
+      </c>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L775" t="inlineStr"/>
+      <c r="M775" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N775" s="2" t="n">
+        <v>45104</v>
+      </c>
+      <c r="O775" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P775" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q775" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R775" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S775" t="inlineStr"/>
+      <c r="T775" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U775" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V775" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA DEL CARIBE</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>Santa Marta</t>
+        </is>
+      </c>
+      <c r="F776" t="n">
+        <v>119366</v>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>INGENIERIA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I776" t="n">
+        <v>174</v>
+      </c>
+      <c r="J776" t="n">
+        <v>10</v>
+      </c>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L776" t="inlineStr"/>
+      <c r="M776" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N776" s="2" t="n">
+        <v>44952</v>
+      </c>
+      <c r="O776" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P776" t="inlineStr">
+        <is>
+          <t>Industria y procesamiento</t>
+        </is>
+      </c>
+      <c r="Q776" t="inlineStr">
+        <is>
+          <t>Industria y procesamiento no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R776" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S776" t="inlineStr"/>
+      <c r="T776" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U776" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V776" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F777" t="n">
+        <v>119302</v>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I777" t="n">
+        <v>154</v>
+      </c>
+      <c r="J777" t="n">
+        <v>9</v>
+      </c>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L777" t="inlineStr"/>
+      <c r="M777" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N777" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="O777" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P777" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q777" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R777" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S777" t="inlineStr"/>
+      <c r="T777" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U777" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V777" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F778" t="n">
+        <v>119303</v>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I778" t="n">
+        <v>154</v>
+      </c>
+      <c r="J778" t="n">
+        <v>9</v>
+      </c>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L778" t="inlineStr"/>
+      <c r="M778" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N778" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="O778" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P778" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q778" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R778" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S778" t="inlineStr"/>
+      <c r="T778" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U778" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V778" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>5801</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>CORPORACION ESCUELA TECNOLOGICA DEL ORIENTE</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F779" t="n">
+        <v>119385</v>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>DERECHO</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I779" t="n">
+        <v>159</v>
+      </c>
+      <c r="J779" t="n">
+        <v>9</v>
+      </c>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L779" t="inlineStr"/>
+      <c r="M779" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N779" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O779" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P779" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q779" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R779" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S779" t="inlineStr"/>
+      <c r="T779" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U779" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V779" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>9913</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DE ASTURIAS</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F780" t="n">
+        <v>119320</v>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I780" t="n">
+        <v>147</v>
+      </c>
+      <c r="J780" t="n">
+        <v>9</v>
+      </c>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L780" t="inlineStr"/>
+      <c r="M780" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N780" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O780" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P780" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q780" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R780" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S780" t="inlineStr"/>
+      <c r="T780" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U780" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V780" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>9945</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN UNIVERSITARIA DE BOGOTA -UNIVERSITARIA DE BOGOTÁ</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F781" t="n">
+        <v>119342</v>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>INGENIERÍA CIVIL</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I781" t="n">
+        <v>154</v>
+      </c>
+      <c r="J781" t="n">
+        <v>9</v>
+      </c>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L781" t="inlineStr"/>
+      <c r="M781" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N781" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="O781" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P781" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q781" t="inlineStr">
+        <is>
+          <t>Construcción e ingeniería civil</t>
+        </is>
+      </c>
+      <c r="R781" t="inlineStr">
+        <is>
+          <t>Ingeniería civil y afines</t>
+        </is>
+      </c>
+      <c r="S781" t="inlineStr"/>
+      <c r="T781" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U781" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V781" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>9945</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN UNIVERSITARIA DE BOGOTA -UNIVERSITARIA DE BOGOTÁ</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F782" t="n">
+        <v>119343</v>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>INGENIERÍA CIVIL</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I782" t="n">
+        <v>154</v>
+      </c>
+      <c r="J782" t="n">
+        <v>9</v>
+      </c>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L782" t="inlineStr"/>
+      <c r="M782" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N782" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="O782" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P782" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q782" t="inlineStr">
+        <is>
+          <t>Construcción e ingeniería civil</t>
+        </is>
+      </c>
+      <c r="R782" t="inlineStr">
+        <is>
+          <t>Ingeniería civil y afines</t>
+        </is>
+      </c>
+      <c r="S782" t="inlineStr"/>
+      <c r="T782" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U782" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V782" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>9946</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA PÚBLICA DE BELLO - IUPBELLO</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="F783" t="n">
+        <v>119308</v>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE NEGOCIOS</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I783" t="n">
+        <v>144</v>
+      </c>
+      <c r="J783" t="n">
+        <v>8</v>
+      </c>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L783" t="inlineStr"/>
+      <c r="M783" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N783" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="O783" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P783" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q783" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R783" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S783" t="inlineStr"/>
+      <c r="T783" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U783" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V783" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V783"/>
+  <dimension ref="A1:V810"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73778,10 +73778,8 @@
       </c>
     </row>
     <row r="758">
-      <c r="A758" t="inlineStr">
-        <is>
-          <t>1207</t>
-        </is>
+      <c r="A758" t="n">
+        <v>1207</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
@@ -73833,7 +73831,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N758" s="2" t="n">
+      <c r="N758" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="O758" t="inlineStr">
@@ -73874,10 +73872,8 @@
       </c>
     </row>
     <row r="759">
-      <c r="A759" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A759" t="n">
+        <v>1709</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
@@ -73929,7 +73925,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N759" s="2" t="n">
+      <c r="N759" s="1" t="n">
         <v>45906</v>
       </c>
       <c r="O759" t="inlineStr">
@@ -73970,10 +73966,8 @@
       </c>
     </row>
     <row r="760">
-      <c r="A760" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A760" t="n">
+        <v>1729</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
@@ -74025,7 +74019,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N760" s="2" t="n">
+      <c r="N760" s="1" t="n">
         <v>46224</v>
       </c>
       <c r="O760" t="inlineStr">
@@ -74066,10 +74060,8 @@
       </c>
     </row>
     <row r="761">
-      <c r="A761" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
+      <c r="A761" t="n">
+        <v>1805</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
@@ -74121,7 +74113,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N761" s="2" t="n">
+      <c r="N761" s="1" t="n">
         <v>46224</v>
       </c>
       <c r="O761" t="inlineStr">
@@ -74162,10 +74154,8 @@
       </c>
     </row>
     <row r="762">
-      <c r="A762" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
+      <c r="A762" t="n">
+        <v>1826</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
@@ -74217,7 +74207,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N762" s="2" t="n">
+      <c r="N762" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O762" t="inlineStr">
@@ -74258,10 +74248,8 @@
       </c>
     </row>
     <row r="763">
-      <c r="A763" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
+      <c r="A763" t="n">
+        <v>1826</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
@@ -74313,7 +74301,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N763" s="2" t="n">
+      <c r="N763" s="1" t="n">
         <v>46209</v>
       </c>
       <c r="O763" t="inlineStr">
@@ -74354,10 +74342,8 @@
       </c>
     </row>
     <row r="764">
-      <c r="A764" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
+      <c r="A764" t="n">
+        <v>1826</v>
       </c>
       <c r="B764" t="inlineStr">
         <is>
@@ -74409,7 +74395,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N764" s="2" t="n">
+      <c r="N764" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O764" t="inlineStr">
@@ -74450,10 +74436,8 @@
       </c>
     </row>
     <row r="765">
-      <c r="A765" t="inlineStr">
-        <is>
-          <t>2110</t>
-        </is>
+      <c r="A765" t="n">
+        <v>2110</v>
       </c>
       <c r="B765" t="inlineStr">
         <is>
@@ -74505,7 +74489,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N765" s="2" t="n">
+      <c r="N765" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="O765" t="inlineStr">
@@ -74546,10 +74530,8 @@
       </c>
     </row>
     <row r="766">
-      <c r="A766" t="inlineStr">
-        <is>
-          <t>2746</t>
-        </is>
+      <c r="A766" t="n">
+        <v>2746</v>
       </c>
       <c r="B766" t="inlineStr">
         <is>
@@ -74601,7 +74583,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N766" s="2" t="n">
+      <c r="N766" s="1" t="n">
         <v>46224</v>
       </c>
       <c r="O766" t="inlineStr">
@@ -74642,10 +74624,8 @@
       </c>
     </row>
     <row r="767">
-      <c r="A767" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A767" t="n">
+        <v>2829</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
@@ -74697,7 +74677,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N767" s="2" t="n">
+      <c r="N767" s="1" t="n">
         <v>46154</v>
       </c>
       <c r="O767" t="inlineStr">
@@ -74738,10 +74718,8 @@
       </c>
     </row>
     <row r="768">
-      <c r="A768" t="inlineStr">
-        <is>
-          <t>2837</t>
-        </is>
+      <c r="A768" t="n">
+        <v>2837</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
@@ -74793,7 +74771,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N768" s="2" t="n">
+      <c r="N768" s="1" t="n">
         <v>44589</v>
       </c>
       <c r="O768" t="inlineStr">
@@ -74834,10 +74812,8 @@
       </c>
     </row>
     <row r="769">
-      <c r="A769" t="inlineStr">
-        <is>
-          <t>3117</t>
-        </is>
+      <c r="A769" t="n">
+        <v>3117</v>
       </c>
       <c r="B769" t="inlineStr">
         <is>
@@ -74889,7 +74865,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N769" s="2" t="n">
+      <c r="N769" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="O769" t="inlineStr">
@@ -74930,10 +74906,8 @@
       </c>
     </row>
     <row r="770">
-      <c r="A770" t="inlineStr">
-        <is>
-          <t>3201</t>
-        </is>
+      <c r="A770" t="n">
+        <v>3201</v>
       </c>
       <c r="B770" t="inlineStr">
         <is>
@@ -74985,7 +74959,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N770" s="2" t="n">
+      <c r="N770" s="1" t="n">
         <v>46233</v>
       </c>
       <c r="O770" t="inlineStr">
@@ -75026,10 +75000,8 @@
       </c>
     </row>
     <row r="771">
-      <c r="A771" t="inlineStr">
-        <is>
-          <t>3303</t>
-        </is>
+      <c r="A771" t="n">
+        <v>3303</v>
       </c>
       <c r="B771" t="inlineStr">
         <is>
@@ -75081,7 +75053,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N771" s="2" t="n">
+      <c r="N771" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O771" t="inlineStr">
@@ -75122,10 +75094,8 @@
       </c>
     </row>
     <row r="772">
-      <c r="A772" t="inlineStr">
-        <is>
-          <t>3821</t>
-        </is>
+      <c r="A772" t="n">
+        <v>3821</v>
       </c>
       <c r="B772" t="inlineStr">
         <is>
@@ -75177,7 +75147,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N772" s="2" t="n">
+      <c r="N772" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="O772" t="inlineStr">
@@ -75218,10 +75188,8 @@
       </c>
     </row>
     <row r="773">
-      <c r="A773" t="inlineStr">
-        <is>
-          <t>4102</t>
-        </is>
+      <c r="A773" t="n">
+        <v>4102</v>
       </c>
       <c r="B773" t="inlineStr">
         <is>
@@ -75273,7 +75241,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N773" s="2" t="n">
+      <c r="N773" s="1" t="n">
         <v>46106</v>
       </c>
       <c r="O773" t="inlineStr">
@@ -75314,10 +75282,8 @@
       </c>
     </row>
     <row r="774">
-      <c r="A774" t="inlineStr">
-        <is>
-          <t>4111</t>
-        </is>
+      <c r="A774" t="n">
+        <v>4111</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
@@ -75369,7 +75335,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N774" s="2" t="n">
+      <c r="N774" s="1" t="n">
         <v>45104</v>
       </c>
       <c r="O774" t="inlineStr">
@@ -75410,10 +75376,8 @@
       </c>
     </row>
     <row r="775">
-      <c r="A775" t="inlineStr">
-        <is>
-          <t>4111</t>
-        </is>
+      <c r="A775" t="n">
+        <v>4111</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
@@ -75465,7 +75429,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N775" s="2" t="n">
+      <c r="N775" s="1" t="n">
         <v>45104</v>
       </c>
       <c r="O775" t="inlineStr">
@@ -75506,10 +75470,8 @@
       </c>
     </row>
     <row r="776">
-      <c r="A776" t="inlineStr">
-        <is>
-          <t>4111</t>
-        </is>
+      <c r="A776" t="n">
+        <v>4111</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
@@ -75561,7 +75523,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N776" s="2" t="n">
+      <c r="N776" s="1" t="n">
         <v>44952</v>
       </c>
       <c r="O776" t="inlineStr">
@@ -75602,10 +75564,8 @@
       </c>
     </row>
     <row r="777">
-      <c r="A777" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A777" t="n">
+        <v>4813</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
@@ -75657,7 +75617,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N777" s="2" t="n">
+      <c r="N777" s="1" t="n">
         <v>46183</v>
       </c>
       <c r="O777" t="inlineStr">
@@ -75698,10 +75658,8 @@
       </c>
     </row>
     <row r="778">
-      <c r="A778" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A778" t="n">
+        <v>4813</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
@@ -75753,7 +75711,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N778" s="2" t="n">
+      <c r="N778" s="1" t="n">
         <v>46183</v>
       </c>
       <c r="O778" t="inlineStr">
@@ -75794,10 +75752,8 @@
       </c>
     </row>
     <row r="779">
-      <c r="A779" t="inlineStr">
-        <is>
-          <t>5801</t>
-        </is>
+      <c r="A779" t="n">
+        <v>5801</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
@@ -75849,7 +75805,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N779" s="2" t="n">
+      <c r="N779" s="1" t="n">
         <v>46154</v>
       </c>
       <c r="O779" t="inlineStr">
@@ -75890,10 +75846,8 @@
       </c>
     </row>
     <row r="780">
-      <c r="A780" t="inlineStr">
-        <is>
-          <t>9913</t>
-        </is>
+      <c r="A780" t="n">
+        <v>9913</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
@@ -75945,7 +75899,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N780" s="2" t="n">
+      <c r="N780" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="O780" t="inlineStr">
@@ -75986,10 +75940,8 @@
       </c>
     </row>
     <row r="781">
-      <c r="A781" t="inlineStr">
-        <is>
-          <t>9945</t>
-        </is>
+      <c r="A781" t="n">
+        <v>9945</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
@@ -76041,7 +75993,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N781" s="2" t="n">
+      <c r="N781" s="1" t="n">
         <v>46184</v>
       </c>
       <c r="O781" t="inlineStr">
@@ -76082,10 +76034,8 @@
       </c>
     </row>
     <row r="782">
-      <c r="A782" t="inlineStr">
-        <is>
-          <t>9945</t>
-        </is>
+      <c r="A782" t="n">
+        <v>9945</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
@@ -76137,7 +76087,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N782" s="2" t="n">
+      <c r="N782" s="1" t="n">
         <v>46184</v>
       </c>
       <c r="O782" t="inlineStr">
@@ -76178,10 +76128,8 @@
       </c>
     </row>
     <row r="783">
-      <c r="A783" t="inlineStr">
-        <is>
-          <t>9946</t>
-        </is>
+      <c r="A783" t="n">
+        <v>9946</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
@@ -76233,7 +76181,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N783" s="2" t="n">
+      <c r="N783" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="O783" t="inlineStr">
@@ -76268,6 +76216,2598 @@
         </is>
       </c>
       <c r="V783" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PEDAGOGICA Y TECNOLOGICA DE COLOMBIA - UPTC</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F784" t="n">
+        <v>119491</v>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN CONSTRUCCIÓN</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>Híbrida (A distancia-Virtual)</t>
+        </is>
+      </c>
+      <c r="I784" t="n">
+        <v>153</v>
+      </c>
+      <c r="J784" t="n">
+        <v>10</v>
+      </c>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L784" t="inlineStr"/>
+      <c r="M784" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N784" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="O784" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P784" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q784" t="inlineStr">
+        <is>
+          <t>Construcción e ingeniería civil</t>
+        </is>
+      </c>
+      <c r="R784" t="inlineStr">
+        <is>
+          <t>Ingeniería civil y afines</t>
+        </is>
+      </c>
+      <c r="S784" t="inlineStr"/>
+      <c r="T784" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U784" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V784" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>1702</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>PONTIFICIA UNIVERSIDAD JAVERIANA</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F785" t="n">
+        <v>119340</v>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>INGENIERÍA ROBÓTICA</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I785" t="n">
+        <v>150</v>
+      </c>
+      <c r="J785" t="n">
+        <v>9</v>
+      </c>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L785" t="inlineStr"/>
+      <c r="M785" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N785" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O785" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P785" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q785" t="inlineStr">
+        <is>
+          <t>Electrónica y automatización</t>
+        </is>
+      </c>
+      <c r="R785" t="inlineStr">
+        <is>
+          <t>Ingeniería electrónica, telecomunicaciones y afines</t>
+        </is>
+      </c>
+      <c r="S785" t="inlineStr"/>
+      <c r="T785" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U785" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V785" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>1703</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD INCCA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F786" t="n">
+        <v>119405</v>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>CONTADURÍA PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I786" t="n">
+        <v>144</v>
+      </c>
+      <c r="J786" t="n">
+        <v>9</v>
+      </c>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L786" t="inlineStr"/>
+      <c r="M786" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N786" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O786" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P786" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q786" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R786" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S786" t="inlineStr"/>
+      <c r="T786" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U786" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V786" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>1716</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SAN BUENAVENTURA</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F787" t="n">
+        <v>119441</v>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>DANZA Y PERFORMANCE</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I787" t="n">
+        <v>138</v>
+      </c>
+      <c r="J787" t="n">
+        <v>8</v>
+      </c>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L787" t="inlineStr"/>
+      <c r="M787" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N787" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="O787" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P787" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q787" t="inlineStr">
+        <is>
+          <t>Bellas artes</t>
+        </is>
+      </c>
+      <c r="R787" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="S787" t="inlineStr"/>
+      <c r="T787" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U787" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V787" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>1725</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD AUTONOMA DE COLOMBIA -FUAC-</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F788" t="n">
+        <v>119406</v>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>RELACIONES ECONÓMICAS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I788" t="n">
+        <v>146</v>
+      </c>
+      <c r="J788" t="n">
+        <v>8</v>
+      </c>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L788" t="inlineStr"/>
+      <c r="M788" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N788" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="O788" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P788" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q788" t="inlineStr">
+        <is>
+          <t>Ciencias políticas y educación cívica</t>
+        </is>
+      </c>
+      <c r="R788" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S788" t="inlineStr"/>
+      <c r="T788" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U788" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V788" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>1816</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F789" t="n">
+        <v>119423</v>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I789" t="n">
+        <v>144</v>
+      </c>
+      <c r="J789" t="n">
+        <v>8</v>
+      </c>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L789" t="inlineStr"/>
+      <c r="M789" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N789" s="2" t="n">
+        <v>45103</v>
+      </c>
+      <c r="O789" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P789" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q789" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R789" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S789" t="inlineStr"/>
+      <c r="T789" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U789" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V789" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F790" t="n">
+        <v>119429</v>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>DISEÑO CROSSMEDIA</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I790" t="n">
+        <v>136</v>
+      </c>
+      <c r="J790" t="n">
+        <v>8</v>
+      </c>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L790" t="inlineStr"/>
+      <c r="M790" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N790" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="O790" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P790" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q790" t="inlineStr">
+        <is>
+          <t>Técnicas audiovisuales y producción para medios de comunicación</t>
+        </is>
+      </c>
+      <c r="R790" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S790" t="inlineStr"/>
+      <c r="T790" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U790" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="V790" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE BUCARAMANGA-UNAB-</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F791" t="n">
+        <v>119461</v>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>ARTES ESCÉNICAS</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I791" t="n">
+        <v>137</v>
+      </c>
+      <c r="J791" t="n">
+        <v>8</v>
+      </c>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L791" t="inlineStr"/>
+      <c r="M791" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N791" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="O791" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P791" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q791" t="inlineStr">
+        <is>
+          <t>Música y artes escénicas</t>
+        </is>
+      </c>
+      <c r="R791" t="inlineStr">
+        <is>
+          <t>Artes representativas</t>
+        </is>
+      </c>
+      <c r="S791" t="inlineStr"/>
+      <c r="T791" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U791" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="V791" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>1827</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CATOLICA DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F792" t="n">
+        <v>119488</v>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE EMPRESAS TURÍSTICAS</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I792" t="n">
+        <v>137</v>
+      </c>
+      <c r="J792" t="n">
+        <v>8</v>
+      </c>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L792" t="inlineStr"/>
+      <c r="M792" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N792" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="O792" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P792" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q792" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R792" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S792" t="inlineStr"/>
+      <c r="T792" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U792" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V792" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2707</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>FUNDACIÓN UNIVERSITARIA JUAN N. CORPAS</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F793" t="n">
+        <v>119444</v>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>MEDICINA</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I793" t="n">
+        <v>292</v>
+      </c>
+      <c r="J793" t="n">
+        <v>12</v>
+      </c>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L793" t="inlineStr"/>
+      <c r="M793" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N793" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="O793" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P793" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q793" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R793" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S793" t="inlineStr"/>
+      <c r="T793" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U793" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V793" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F794" t="n">
+        <v>119464</v>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>CONTADURÍA PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I794" t="n">
+        <v>140</v>
+      </c>
+      <c r="J794" t="n">
+        <v>9</v>
+      </c>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L794" t="inlineStr"/>
+      <c r="M794" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N794" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="O794" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P794" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q794" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R794" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S794" t="inlineStr"/>
+      <c r="T794" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U794" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V794" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F795" t="n">
+        <v>119490</v>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>INGENIERÍA MECATRÓNICA</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I795" t="n">
+        <v>142</v>
+      </c>
+      <c r="J795" t="n">
+        <v>9</v>
+      </c>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L795" t="inlineStr"/>
+      <c r="M795" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N795" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="O795" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P795" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q795" t="inlineStr">
+        <is>
+          <t>Electrónica y automatización</t>
+        </is>
+      </c>
+      <c r="R795" t="inlineStr">
+        <is>
+          <t>Ingeniería electrónica, telecomunicaciones y afines</t>
+        </is>
+      </c>
+      <c r="S795" t="inlineStr"/>
+      <c r="T795" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U795" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V795" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F796" t="n">
+        <v>119434</v>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN CIENCIAS NATURALES Y EDUCACIÓN AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I796" t="n">
+        <v>144</v>
+      </c>
+      <c r="J796" t="n">
+        <v>10</v>
+      </c>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L796" t="inlineStr"/>
+      <c r="M796" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N796" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="O796" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P796" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q796" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R796" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S796" t="inlineStr"/>
+      <c r="T796" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U796" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V796" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F797" t="n">
+        <v>119435</v>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN DISEÑO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I797" t="n">
+        <v>144</v>
+      </c>
+      <c r="J797" t="n">
+        <v>10</v>
+      </c>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L797" t="inlineStr"/>
+      <c r="M797" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N797" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="O797" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P797" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q797" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R797" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S797" t="inlineStr"/>
+      <c r="T797" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U797" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V797" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>Duitama</t>
+        </is>
+      </c>
+      <c r="F798" t="n">
+        <v>119445</v>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN EDUCACIÓN FÍSICA, RECREACIÓN Y DEPORTES</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I798" t="n">
+        <v>144</v>
+      </c>
+      <c r="J798" t="n">
+        <v>8</v>
+      </c>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L798" t="inlineStr"/>
+      <c r="M798" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N798" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="O798" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P798" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q798" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R798" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S798" t="inlineStr"/>
+      <c r="T798" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U798" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V798" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>Duitama</t>
+        </is>
+      </c>
+      <c r="F799" t="n">
+        <v>119421</v>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>TRABAJO SOCIAL</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I799" t="n">
+        <v>144</v>
+      </c>
+      <c r="J799" t="n">
+        <v>8</v>
+      </c>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L799" t="inlineStr"/>
+      <c r="M799" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N799" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="O799" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P799" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q799" t="inlineStr">
+        <is>
+          <t>Trabajo social</t>
+        </is>
+      </c>
+      <c r="R799" t="inlineStr">
+        <is>
+          <t>Sociología, trabajo social y afines</t>
+        </is>
+      </c>
+      <c r="S799" t="inlineStr"/>
+      <c r="T799" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U799" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V799" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2830</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA IBEROAMERICANA</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F800" t="n">
+        <v>119462</v>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>DISEÑO VISUAL</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I800" t="n">
+        <v>144</v>
+      </c>
+      <c r="J800" t="n">
+        <v>8</v>
+      </c>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L800" t="inlineStr"/>
+      <c r="M800" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N800" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="O800" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P800" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q800" t="inlineStr">
+        <is>
+          <t>Técnicas audiovisuales y producción para medios de comunicación</t>
+        </is>
+      </c>
+      <c r="R800" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S800" t="inlineStr"/>
+      <c r="T800" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U800" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="V800" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>3117</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA DE BARRANQUILLA - IUB</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F801" t="n">
+        <v>119450</v>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN TECNOLOGÍA E INFORMÁTICA</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I801" t="n">
+        <v>165</v>
+      </c>
+      <c r="J801" t="n">
+        <v>13</v>
+      </c>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L801" t="inlineStr"/>
+      <c r="M801" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N801" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="O801" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P801" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q801" t="inlineStr">
+        <is>
+          <t>Formación para docentes con asignatura de especialización</t>
+        </is>
+      </c>
+      <c r="R801" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S801" t="inlineStr"/>
+      <c r="T801" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U801" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V801" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>TECNOLÓGICO DE ARTES DÉBORA ARANGO INSTITUCIÓN REDEFINIDA</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F802" t="n">
+        <v>119446</v>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>PROFESIONAL UNIVERSITARIO EN PROYECTOS, MARKETING Y NUEVAS TECNOLOGÍAS PARA LA GESTIÓN CULTURAL</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I802" t="n">
+        <v>148</v>
+      </c>
+      <c r="J802" t="n">
+        <v>8</v>
+      </c>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L802" t="inlineStr"/>
+      <c r="M802" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N802" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="O802" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P802" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q802" t="inlineStr">
+        <is>
+          <t>Artes no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R802" t="inlineStr">
+        <is>
+          <t>Otros programas asociados a bellas artes</t>
+        </is>
+      </c>
+      <c r="S802" t="inlineStr"/>
+      <c r="T802" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U802" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V802" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>TECNOLÓGICO DE ARTES DÉBORA ARANGO INSTITUCIÓN REDEFINIDA</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F803" t="n">
+        <v>119447</v>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>PROFESIONAL UNIVERSITARIO EN PROYECTOS, MARKETING Y NUEVAS TECNOLOGÍAS PARA LA GESTIÓN CULTURAL</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I803" t="n">
+        <v>148</v>
+      </c>
+      <c r="J803" t="n">
+        <v>8</v>
+      </c>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L803" t="inlineStr"/>
+      <c r="M803" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N803" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="O803" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P803" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q803" t="inlineStr">
+        <is>
+          <t>Artes no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R803" t="inlineStr">
+        <is>
+          <t>Otros programas asociados a bellas artes</t>
+        </is>
+      </c>
+      <c r="S803" t="inlineStr"/>
+      <c r="T803" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U803" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V803" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F804" t="n">
+        <v>119414</v>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN AGROINDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I804" t="n">
+        <v>154</v>
+      </c>
+      <c r="J804" t="n">
+        <v>9</v>
+      </c>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L804" t="inlineStr"/>
+      <c r="M804" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N804" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="O804" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P804" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q804" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R804" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S804" t="inlineStr"/>
+      <c r="T804" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U804" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V804" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F805" t="n">
+        <v>119478</v>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE EMPRESAS TURÍSTICAS Y HOTELERAS</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I805" t="n">
+        <v>155</v>
+      </c>
+      <c r="J805" t="n">
+        <v>9</v>
+      </c>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L805" t="inlineStr"/>
+      <c r="M805" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N805" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="O805" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P805" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q805" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R805" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S805" t="inlineStr"/>
+      <c r="T805" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U805" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V805" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F806" t="n">
+        <v>119479</v>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE EMPRESAS TURÍSTICAS Y HOTELERAS</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I806" t="n">
+        <v>155</v>
+      </c>
+      <c r="J806" t="n">
+        <v>9</v>
+      </c>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L806" t="inlineStr"/>
+      <c r="M806" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N806" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="O806" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P806" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q806" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R806" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S806" t="inlineStr"/>
+      <c r="T806" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U806" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V806" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F807" t="n">
+        <v>119481</v>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>INGENIERÍA QUÍMICA</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I807" t="n">
+        <v>156</v>
+      </c>
+      <c r="J807" t="n">
+        <v>9</v>
+      </c>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L807" t="inlineStr"/>
+      <c r="M807" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N807" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="O807" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P807" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q807" t="inlineStr">
+        <is>
+          <t>Ingeniería y procesos químicos</t>
+        </is>
+      </c>
+      <c r="R807" t="inlineStr">
+        <is>
+          <t>Ingeniería química y afines</t>
+        </is>
+      </c>
+      <c r="S807" t="inlineStr"/>
+      <c r="T807" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U807" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V807" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>ESCUELA MILITAR DE AVIACION MARCO FIDEL SUAREZ</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F808" t="n">
+        <v>119439</v>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>INGENIERIA EN SISTEMAS AEROESPACIALES</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I808" t="n">
+        <v>160</v>
+      </c>
+      <c r="J808" t="n">
+        <v>8</v>
+      </c>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L808" t="inlineStr"/>
+      <c r="M808" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N808" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="O808" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P808" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q808" t="inlineStr">
+        <is>
+          <t>Vehículos, barcos y aeronaves de motor</t>
+        </is>
+      </c>
+      <c r="R808" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S808" t="inlineStr"/>
+      <c r="T808" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U808" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V808" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>9899</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE COLOMBIA - UNIVERSITARIA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F809" t="n">
+        <v>119485</v>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>DERECHO</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I809" t="n">
+        <v>160</v>
+      </c>
+      <c r="J809" t="n">
+        <v>10</v>
+      </c>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L809" t="inlineStr"/>
+      <c r="M809" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N809" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="O809" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P809" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q809" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R809" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S809" t="inlineStr"/>
+      <c r="T809" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U809" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V809" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>9915</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>UNIVERSITARIA VIRTUAL INTERNACIONAL</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F810" t="n">
+        <v>119455</v>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I810" t="n">
+        <v>153</v>
+      </c>
+      <c r="J810" t="n">
+        <v>18</v>
+      </c>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="L810" t="inlineStr"/>
+      <c r="M810" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N810" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="O810" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P810" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q810" t="inlineStr">
+        <is>
+          <t>Electrónica y automatización</t>
+        </is>
+      </c>
+      <c r="R810" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S810" t="inlineStr"/>
+      <c r="T810" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="U810" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V810" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V810"/>
+  <dimension ref="A1:V821"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76222,10 +76222,8 @@
       </c>
     </row>
     <row r="784">
-      <c r="A784" t="inlineStr">
-        <is>
-          <t>1106</t>
-        </is>
+      <c r="A784" t="n">
+        <v>1106</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
@@ -76277,7 +76275,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N784" s="2" t="n">
+      <c r="N784" s="1" t="n">
         <v>46211</v>
       </c>
       <c r="O784" t="inlineStr">
@@ -76318,10 +76316,8 @@
       </c>
     </row>
     <row r="785">
-      <c r="A785" t="inlineStr">
-        <is>
-          <t>1702</t>
-        </is>
+      <c r="A785" t="n">
+        <v>1702</v>
       </c>
       <c r="B785" t="inlineStr">
         <is>
@@ -76373,7 +76369,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N785" s="2" t="n">
+      <c r="N785" s="1" t="n">
         <v>46154</v>
       </c>
       <c r="O785" t="inlineStr">
@@ -76414,10 +76410,8 @@
       </c>
     </row>
     <row r="786">
-      <c r="A786" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
+      <c r="A786" t="n">
+        <v>1703</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
@@ -76469,7 +76463,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N786" s="2" t="n">
+      <c r="N786" s="1" t="n">
         <v>46154</v>
       </c>
       <c r="O786" t="inlineStr">
@@ -76510,10 +76504,8 @@
       </c>
     </row>
     <row r="787">
-      <c r="A787" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A787" t="n">
+        <v>1716</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
@@ -76565,7 +76557,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N787" s="2" t="n">
+      <c r="N787" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="O787" t="inlineStr">
@@ -76606,10 +76598,8 @@
       </c>
     </row>
     <row r="788">
-      <c r="A788" t="inlineStr">
-        <is>
-          <t>1725</t>
-        </is>
+      <c r="A788" t="n">
+        <v>1725</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
@@ -76661,7 +76651,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N788" s="2" t="n">
+      <c r="N788" s="1" t="n">
         <v>46183</v>
       </c>
       <c r="O788" t="inlineStr">
@@ -76702,10 +76692,8 @@
       </c>
     </row>
     <row r="789">
-      <c r="A789" t="inlineStr">
-        <is>
-          <t>1816</t>
-        </is>
+      <c r="A789" t="n">
+        <v>1816</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
@@ -76757,7 +76745,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N789" s="2" t="n">
+      <c r="N789" s="1" t="n">
         <v>45103</v>
       </c>
       <c r="O789" t="inlineStr">
@@ -76798,10 +76786,8 @@
       </c>
     </row>
     <row r="790">
-      <c r="A790" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A790" t="n">
+        <v>1818</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
@@ -76853,7 +76839,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N790" s="2" t="n">
+      <c r="N790" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="O790" t="inlineStr">
@@ -76894,10 +76880,8 @@
       </c>
     </row>
     <row r="791">
-      <c r="A791" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A791" t="n">
+        <v>1823</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
@@ -76949,7 +76933,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N791" s="2" t="n">
+      <c r="N791" s="1" t="n">
         <v>46224</v>
       </c>
       <c r="O791" t="inlineStr">
@@ -76990,10 +76974,8 @@
       </c>
     </row>
     <row r="792">
-      <c r="A792" t="inlineStr">
-        <is>
-          <t>1827</t>
-        </is>
+      <c r="A792" t="n">
+        <v>1827</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
@@ -77045,7 +77027,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N792" s="2" t="n">
+      <c r="N792" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="O792" t="inlineStr">
@@ -77086,10 +77068,8 @@
       </c>
     </row>
     <row r="793">
-      <c r="A793" t="inlineStr">
-        <is>
-          <t>2707</t>
-        </is>
+      <c r="A793" t="n">
+        <v>2707</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
@@ -77141,7 +77121,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N793" s="2" t="n">
+      <c r="N793" s="1" t="n">
         <v>46184</v>
       </c>
       <c r="O793" t="inlineStr">
@@ -77182,10 +77162,8 @@
       </c>
     </row>
     <row r="794">
-      <c r="A794" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A794" t="n">
+        <v>2829</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
@@ -77237,7 +77215,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N794" s="2" t="n">
+      <c r="N794" s="1" t="n">
         <v>46224</v>
       </c>
       <c r="O794" t="inlineStr">
@@ -77278,10 +77256,8 @@
       </c>
     </row>
     <row r="795">
-      <c r="A795" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A795" t="n">
+        <v>2829</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
@@ -77333,7 +77309,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N795" s="2" t="n">
+      <c r="N795" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="O795" t="inlineStr">
@@ -77374,10 +77350,8 @@
       </c>
     </row>
     <row r="796">
-      <c r="A796" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A796" t="n">
+        <v>2829</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
@@ -77429,7 +77403,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N796" s="2" t="n">
+      <c r="N796" s="1" t="n">
         <v>46184</v>
       </c>
       <c r="O796" t="inlineStr">
@@ -77470,10 +77444,8 @@
       </c>
     </row>
     <row r="797">
-      <c r="A797" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A797" t="n">
+        <v>2829</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
@@ -77525,7 +77497,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N797" s="2" t="n">
+      <c r="N797" s="1" t="n">
         <v>46184</v>
       </c>
       <c r="O797" t="inlineStr">
@@ -77566,10 +77538,8 @@
       </c>
     </row>
     <row r="798">
-      <c r="A798" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A798" t="n">
+        <v>2829</v>
       </c>
       <c r="B798" t="inlineStr">
         <is>
@@ -77621,7 +77591,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N798" s="2" t="n">
+      <c r="N798" s="1" t="n">
         <v>46184</v>
       </c>
       <c r="O798" t="inlineStr">
@@ -77662,10 +77632,8 @@
       </c>
     </row>
     <row r="799">
-      <c r="A799" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A799" t="n">
+        <v>2829</v>
       </c>
       <c r="B799" t="inlineStr">
         <is>
@@ -77717,7 +77685,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N799" s="2" t="n">
+      <c r="N799" s="1" t="n">
         <v>46184</v>
       </c>
       <c r="O799" t="inlineStr">
@@ -77758,10 +77726,8 @@
       </c>
     </row>
     <row r="800">
-      <c r="A800" t="inlineStr">
-        <is>
-          <t>2830</t>
-        </is>
+      <c r="A800" t="n">
+        <v>2830</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
@@ -77813,7 +77779,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N800" s="2" t="n">
+      <c r="N800" s="1" t="n">
         <v>46224</v>
       </c>
       <c r="O800" t="inlineStr">
@@ -77854,10 +77820,8 @@
       </c>
     </row>
     <row r="801">
-      <c r="A801" t="inlineStr">
-        <is>
-          <t>3117</t>
-        </is>
+      <c r="A801" t="n">
+        <v>3117</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
@@ -77909,7 +77873,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N801" s="2" t="n">
+      <c r="N801" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="O801" t="inlineStr">
@@ -77950,10 +77914,8 @@
       </c>
     </row>
     <row r="802">
-      <c r="A802" t="inlineStr">
-        <is>
-          <t>3303</t>
-        </is>
+      <c r="A802" t="n">
+        <v>3303</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
@@ -78005,7 +77967,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N802" s="2" t="n">
+      <c r="N802" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="O802" t="inlineStr">
@@ -78046,10 +78008,8 @@
       </c>
     </row>
     <row r="803">
-      <c r="A803" t="inlineStr">
-        <is>
-          <t>3303</t>
-        </is>
+      <c r="A803" t="n">
+        <v>3303</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
@@ -78101,7 +78061,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N803" s="2" t="n">
+      <c r="N803" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="O803" t="inlineStr">
@@ -78142,10 +78102,8 @@
       </c>
     </row>
     <row r="804">
-      <c r="A804" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A804" t="n">
+        <v>4813</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
@@ -78197,7 +78155,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N804" s="2" t="n">
+      <c r="N804" s="1" t="n">
         <v>46184</v>
       </c>
       <c r="O804" t="inlineStr">
@@ -78238,10 +78196,8 @@
       </c>
     </row>
     <row r="805">
-      <c r="A805" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A805" t="n">
+        <v>4813</v>
       </c>
       <c r="B805" t="inlineStr">
         <is>
@@ -78293,7 +78249,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N805" s="2" t="n">
+      <c r="N805" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="O805" t="inlineStr">
@@ -78334,10 +78290,8 @@
       </c>
     </row>
     <row r="806">
-      <c r="A806" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A806" t="n">
+        <v>4813</v>
       </c>
       <c r="B806" t="inlineStr">
         <is>
@@ -78389,7 +78343,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N806" s="2" t="n">
+      <c r="N806" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="O806" t="inlineStr">
@@ -78430,10 +78384,8 @@
       </c>
     </row>
     <row r="807">
-      <c r="A807" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A807" t="n">
+        <v>4813</v>
       </c>
       <c r="B807" t="inlineStr">
         <is>
@@ -78485,7 +78437,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N807" s="2" t="n">
+      <c r="N807" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="O807" t="inlineStr">
@@ -78526,10 +78478,8 @@
       </c>
     </row>
     <row r="808">
-      <c r="A808" t="inlineStr">
-        <is>
-          <t>9103</t>
-        </is>
+      <c r="A808" t="n">
+        <v>9103</v>
       </c>
       <c r="B808" t="inlineStr">
         <is>
@@ -78581,7 +78531,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N808" s="2" t="n">
+      <c r="N808" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="O808" t="inlineStr">
@@ -78622,10 +78572,8 @@
       </c>
     </row>
     <row r="809">
-      <c r="A809" t="inlineStr">
-        <is>
-          <t>9899</t>
-        </is>
+      <c r="A809" t="n">
+        <v>9899</v>
       </c>
       <c r="B809" t="inlineStr">
         <is>
@@ -78677,7 +78625,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N809" s="2" t="n">
+      <c r="N809" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="O809" t="inlineStr">
@@ -78718,10 +78666,8 @@
       </c>
     </row>
     <row r="810">
-      <c r="A810" t="inlineStr">
-        <is>
-          <t>9915</t>
-        </is>
+      <c r="A810" t="n">
+        <v>9915</v>
       </c>
       <c r="B810" t="inlineStr">
         <is>
@@ -78773,7 +78719,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N810" s="2" t="n">
+      <c r="N810" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="O810" t="inlineStr">
@@ -78808,6 +78754,1062 @@
         </is>
       </c>
       <c r="V810" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL ATLANTICO</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>Puerto Colombia</t>
+        </is>
+      </c>
+      <c r="F811" t="n">
+        <v>119506</v>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I811" t="n">
+        <v>137</v>
+      </c>
+      <c r="J811" t="n">
+        <v>8</v>
+      </c>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L811" t="inlineStr"/>
+      <c r="M811" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N811" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="O811" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P811" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q811" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R811" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S811" t="inlineStr"/>
+      <c r="T811" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="U811" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V811" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>1707</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE BOGOTA - JORGE TADEO LOZANO</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F812" t="n">
+        <v>119528</v>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>CIENCIA DE DATOS Y SIMULACIÓN COMPUTACIONAL</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I812" t="n">
+        <v>125</v>
+      </c>
+      <c r="J812" t="n">
+        <v>8</v>
+      </c>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L812" t="inlineStr"/>
+      <c r="M812" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N812" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="O812" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P812" t="inlineStr">
+        <is>
+          <t>Matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q812" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="R812" t="inlineStr">
+        <is>
+          <t>Matemáticas, estadística y afines</t>
+        </is>
+      </c>
+      <c r="S812" t="inlineStr"/>
+      <c r="T812" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="U812" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="V812" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PONTIFICIA BOLIVARIANA</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F813" t="n">
+        <v>119356</v>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN INTELIGENCIA ARTIFICIAL Y CIENCIA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I813" t="n">
+        <v>133</v>
+      </c>
+      <c r="J813" t="n">
+        <v>8</v>
+      </c>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L813" t="inlineStr"/>
+      <c r="M813" t="inlineStr">
+        <is>
+          <t>Bimensual</t>
+        </is>
+      </c>
+      <c r="N813" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O813" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P813" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q813" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R813" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S813" t="inlineStr"/>
+      <c r="T813" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="U813" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V813" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>COLEGIO MAYOR DE NUESTRA SEÑORA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F814" t="n">
+        <v>119520</v>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>COMUNICACIÓN Y PERIODISMO DIGITAL</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I814" t="n">
+        <v>139</v>
+      </c>
+      <c r="J814" t="n">
+        <v>8</v>
+      </c>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L814" t="inlineStr"/>
+      <c r="M814" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N814" s="2" t="n">
+        <v>45727</v>
+      </c>
+      <c r="O814" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P814" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q814" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R814" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S814" t="inlineStr"/>
+      <c r="T814" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="U814" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V814" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>1733</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>Santa Marta</t>
+        </is>
+      </c>
+      <c r="F815" t="n">
+        <v>119529</v>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>COMUNICACION SOCIAL Y PERIODISMO DIGITAL</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I815" t="n">
+        <v>128</v>
+      </c>
+      <c r="J815" t="n">
+        <v>8</v>
+      </c>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L815" t="inlineStr"/>
+      <c r="M815" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N815" s="2" t="n">
+        <v>45119</v>
+      </c>
+      <c r="O815" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P815" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q815" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R815" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S815" t="inlineStr"/>
+      <c r="T815" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="U815" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V815" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ANTONIO NARIÑO</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F816" t="n">
+        <v>119509</v>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I816" t="n">
+        <v>141</v>
+      </c>
+      <c r="J816" t="n">
+        <v>8</v>
+      </c>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L816" t="inlineStr"/>
+      <c r="M816" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N816" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="O816" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P816" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q816" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R816" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S816" t="inlineStr"/>
+      <c r="T816" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="U816" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V816" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ANTONIO NARIÑO</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="F817" t="n">
+        <v>119501</v>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>INGENIERÍA MECÁNICA</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I817" t="n">
+        <v>142</v>
+      </c>
+      <c r="J817" t="n">
+        <v>8</v>
+      </c>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L817" t="inlineStr"/>
+      <c r="M817" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N817" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="O817" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P817" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q817" t="inlineStr">
+        <is>
+          <t>Mecánica y profesiones afines a la metalistería</t>
+        </is>
+      </c>
+      <c r="R817" t="inlineStr">
+        <is>
+          <t>Ingeniería mecánica y afines</t>
+        </is>
+      </c>
+      <c r="S817" t="inlineStr"/>
+      <c r="T817" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="U817" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V817" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ANTONIO NARIÑO</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F818" t="n">
+        <v>119500</v>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>INGENIERÍA MECÁNICA</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I818" t="n">
+        <v>142</v>
+      </c>
+      <c r="J818" t="n">
+        <v>8</v>
+      </c>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L818" t="inlineStr"/>
+      <c r="M818" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N818" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="O818" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P818" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q818" t="inlineStr">
+        <is>
+          <t>Mecánica y profesiones afines a la metalistería</t>
+        </is>
+      </c>
+      <c r="R818" t="inlineStr">
+        <is>
+          <t>Ingeniería mecánica y afines</t>
+        </is>
+      </c>
+      <c r="S818" t="inlineStr"/>
+      <c r="T818" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="U818" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V818" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DEL AREA ANDINA</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F819" t="n">
+        <v>119497</v>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS Y ANALÍTICA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I819" t="n">
+        <v>138</v>
+      </c>
+      <c r="J819" t="n">
+        <v>8</v>
+      </c>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L819" t="inlineStr"/>
+      <c r="M819" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N819" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="O819" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P819" t="inlineStr">
+        <is>
+          <t>Matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q819" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="R819" t="inlineStr">
+        <is>
+          <t>Matemáticas, estadística y afines</t>
+        </is>
+      </c>
+      <c r="S819" t="inlineStr"/>
+      <c r="T819" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="U819" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="V819" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>TECNOLÓGICO DE ARTES DÉBORA ARANGO INSTITUCIÓN REDEFINIDA</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F820" t="n">
+        <v>119495</v>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>PROFESIONAL UNIVERSITARIO EN CREACIÓN DE CONTENIDOS AUDIOVISUALES</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I820" t="n">
+        <v>154</v>
+      </c>
+      <c r="J820" t="n">
+        <v>8</v>
+      </c>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L820" t="inlineStr"/>
+      <c r="M820" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N820" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="O820" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P820" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q820" t="inlineStr">
+        <is>
+          <t>Técnicas audiovisuales y producción para medios de comunicación</t>
+        </is>
+      </c>
+      <c r="R820" t="inlineStr">
+        <is>
+          <t>Otros programas asociados a bellas artes</t>
+        </is>
+      </c>
+      <c r="S820" t="inlineStr"/>
+      <c r="T820" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="U820" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="V820" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>9902</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA COMFENALCO SANTANDER</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F821" t="n">
+        <v>119519</v>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>DISEÑO DE COMUNICACIÓN VISUAL Y NARRATIVAS DIGITALES</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I821" t="n">
+        <v>124</v>
+      </c>
+      <c r="J821" t="n">
+        <v>8</v>
+      </c>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L821" t="inlineStr"/>
+      <c r="M821" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N821" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="O821" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P821" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q821" t="inlineStr">
+        <is>
+          <t>Técnicas audiovisuales y producción para medios de comunicación</t>
+        </is>
+      </c>
+      <c r="R821" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S821" t="inlineStr"/>
+      <c r="T821" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="U821" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="V821" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V821"/>
+  <dimension ref="A1:V829"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78760,10 +78760,8 @@
       </c>
     </row>
     <row r="811">
-      <c r="A811" t="inlineStr">
-        <is>
-          <t>1202</t>
-        </is>
+      <c r="A811" t="n">
+        <v>1202</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
@@ -78815,7 +78813,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N811" s="2" t="n">
+      <c r="N811" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="O811" t="inlineStr">
@@ -78856,10 +78854,8 @@
       </c>
     </row>
     <row r="812">
-      <c r="A812" t="inlineStr">
-        <is>
-          <t>1707</t>
-        </is>
+      <c r="A812" t="n">
+        <v>1707</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
@@ -78911,7 +78907,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N812" s="2" t="n">
+      <c r="N812" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="O812" t="inlineStr">
@@ -78952,10 +78948,8 @@
       </c>
     </row>
     <row r="813">
-      <c r="A813" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A813" t="n">
+        <v>1710</v>
       </c>
       <c r="B813" t="inlineStr">
         <is>
@@ -79007,7 +79001,7 @@
           <t>Bimensual</t>
         </is>
       </c>
-      <c r="N813" s="2" t="n">
+      <c r="N813" s="1" t="n">
         <v>46154</v>
       </c>
       <c r="O813" t="inlineStr">
@@ -79048,10 +79042,8 @@
       </c>
     </row>
     <row r="814">
-      <c r="A814" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A814" t="n">
+        <v>1714</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
@@ -79103,7 +79095,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N814" s="2" t="n">
+      <c r="N814" s="1" t="n">
         <v>45727</v>
       </c>
       <c r="O814" t="inlineStr">
@@ -79144,10 +79136,8 @@
       </c>
     </row>
     <row r="815">
-      <c r="A815" t="inlineStr">
-        <is>
-          <t>1733</t>
-        </is>
+      <c r="A815" t="n">
+        <v>1733</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
@@ -79199,7 +79189,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N815" s="2" t="n">
+      <c r="N815" s="1" t="n">
         <v>45119</v>
       </c>
       <c r="O815" t="inlineStr">
@@ -79240,10 +79230,8 @@
       </c>
     </row>
     <row r="816">
-      <c r="A816" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
+      <c r="A816" t="n">
+        <v>1826</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
@@ -79295,7 +79283,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N816" s="2" t="n">
+      <c r="N816" s="1" t="n">
         <v>46209</v>
       </c>
       <c r="O816" t="inlineStr">
@@ -79336,10 +79324,8 @@
       </c>
     </row>
     <row r="817">
-      <c r="A817" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
+      <c r="A817" t="n">
+        <v>1826</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
@@ -79391,7 +79377,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N817" s="2" t="n">
+      <c r="N817" s="1" t="n">
         <v>46209</v>
       </c>
       <c r="O817" t="inlineStr">
@@ -79432,10 +79418,8 @@
       </c>
     </row>
     <row r="818">
-      <c r="A818" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
+      <c r="A818" t="n">
+        <v>1826</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
@@ -79487,7 +79471,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N818" s="2" t="n">
+      <c r="N818" s="1" t="n">
         <v>46209</v>
       </c>
       <c r="O818" t="inlineStr">
@@ -79528,10 +79512,8 @@
       </c>
     </row>
     <row r="819">
-      <c r="A819" t="inlineStr">
-        <is>
-          <t>2728</t>
-        </is>
+      <c r="A819" t="n">
+        <v>2728</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
@@ -79583,7 +79565,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N819" s="2" t="n">
+      <c r="N819" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="O819" t="inlineStr">
@@ -79624,10 +79606,8 @@
       </c>
     </row>
     <row r="820">
-      <c r="A820" t="inlineStr">
-        <is>
-          <t>3303</t>
-        </is>
+      <c r="A820" t="n">
+        <v>3303</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
@@ -79679,7 +79659,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N820" s="2" t="n">
+      <c r="N820" s="1" t="n">
         <v>46224</v>
       </c>
       <c r="O820" t="inlineStr">
@@ -79720,10 +79700,8 @@
       </c>
     </row>
     <row r="821">
-      <c r="A821" t="inlineStr">
-        <is>
-          <t>9902</t>
-        </is>
+      <c r="A821" t="n">
+        <v>9902</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
@@ -79775,7 +79753,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N821" s="2" t="n">
+      <c r="N821" s="1" t="n">
         <v>46224</v>
       </c>
       <c r="O821" t="inlineStr">
@@ -79810,6 +79788,776 @@
         </is>
       </c>
       <c r="V821" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F822" t="n">
+        <v>115815</v>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>DERECHO</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I822" t="n">
+        <v>158</v>
+      </c>
+      <c r="J822" t="n">
+        <v>9</v>
+      </c>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L822" t="inlineStr"/>
+      <c r="M822" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N822" s="2" t="n">
+        <v>44672</v>
+      </c>
+      <c r="O822" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P822" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q822" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R822" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S822" t="inlineStr"/>
+      <c r="T822" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="U822" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V822" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE BUCARAMANGA-UNAB-</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F823" t="n">
+        <v>119558</v>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>INGENIERIA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I823" t="n">
+        <v>134</v>
+      </c>
+      <c r="J823" t="n">
+        <v>8</v>
+      </c>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L823" t="inlineStr"/>
+      <c r="M823" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N823" s="2" t="n">
+        <v>44782</v>
+      </c>
+      <c r="O823" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P823" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q823" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R823" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S823" t="inlineStr"/>
+      <c r="T823" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="U823" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V823" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE BUCARAMANGA-UNAB-</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F824" t="n">
+        <v>119547</v>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN CIBERSEGURIDAD</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I824" t="n">
+        <v>132</v>
+      </c>
+      <c r="J824" t="n">
+        <v>8</v>
+      </c>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L824" t="inlineStr"/>
+      <c r="M824" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N824" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="O824" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P824" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q824" t="inlineStr">
+        <is>
+          <t>Diseño y administración de redes y bases de datos</t>
+        </is>
+      </c>
+      <c r="R824" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S824" t="inlineStr"/>
+      <c r="T824" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="U824" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V824" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE BUCARAMANGA-UNAB-</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F825" t="n">
+        <v>119546</v>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN INTELIGENCIA ARTIFICIAL</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I825" t="n">
+        <v>133</v>
+      </c>
+      <c r="J825" t="n">
+        <v>8</v>
+      </c>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L825" t="inlineStr"/>
+      <c r="M825" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N825" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="O825" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P825" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q825" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R825" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S825" t="inlineStr"/>
+      <c r="T825" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="U825" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V825" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DEL AREA ANDINA</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F826" t="n">
+        <v>119545</v>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>CONTADURÍA PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I826" t="n">
+        <v>144</v>
+      </c>
+      <c r="J826" t="n">
+        <v>8</v>
+      </c>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L826" t="inlineStr"/>
+      <c r="M826" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N826" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="O826" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P826" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q826" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R826" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S826" t="inlineStr"/>
+      <c r="T826" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="U826" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V826" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>3115</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA DEL PUTUMAYO</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>Mocoa</t>
+        </is>
+      </c>
+      <c r="F827" t="n">
+        <v>119538</v>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>MEDICINA VETERINARIA</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I827" t="n">
+        <v>169</v>
+      </c>
+      <c r="J827" t="n">
+        <v>10</v>
+      </c>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L827" t="inlineStr"/>
+      <c r="M827" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N827" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="O827" t="inlineStr">
+        <is>
+          <t>Agropecuario, Silvicultura, Pesca y Veterinaria</t>
+        </is>
+      </c>
+      <c r="P827" t="inlineStr">
+        <is>
+          <t>Veterinaria</t>
+        </is>
+      </c>
+      <c r="Q827" t="inlineStr">
+        <is>
+          <t>Veterinaria</t>
+        </is>
+      </c>
+      <c r="R827" t="inlineStr">
+        <is>
+          <t>Medicina veterinaria</t>
+        </is>
+      </c>
+      <c r="S827" t="inlineStr"/>
+      <c r="T827" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="U827" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V827" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA DEL CARIBE</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>Aracataca</t>
+        </is>
+      </c>
+      <c r="F828" t="n">
+        <v>119556</v>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>ADMINISTRACION LOGISTICA</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I828" t="n">
+        <v>188</v>
+      </c>
+      <c r="J828" t="n">
+        <v>10</v>
+      </c>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L828" t="inlineStr"/>
+      <c r="M828" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N828" s="2" t="n">
+        <v>45104</v>
+      </c>
+      <c r="O828" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P828" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q828" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R828" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S828" t="inlineStr"/>
+      <c r="T828" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="U828" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V828" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>4721</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA HORIZONTE</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F829" t="n">
+        <v>107213</v>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>DERECHO</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I829" t="n">
+        <v>155</v>
+      </c>
+      <c r="J829" t="n">
+        <v>9</v>
+      </c>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L829" t="n">
+        <v>5826000</v>
+      </c>
+      <c r="M829" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N829" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="O829" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P829" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q829" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R829" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S829" t="inlineStr"/>
+      <c r="T829" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="U829" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V829" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V829"/>
+  <dimension ref="A1:V834"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79794,10 +79794,8 @@
       </c>
     </row>
     <row r="822">
-      <c r="A822" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A822" t="n">
+        <v>1818</v>
       </c>
       <c r="B822" t="inlineStr">
         <is>
@@ -79849,7 +79847,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N822" s="2" t="n">
+      <c r="N822" s="1" t="n">
         <v>44672</v>
       </c>
       <c r="O822" t="inlineStr">
@@ -79890,10 +79888,8 @@
       </c>
     </row>
     <row r="823">
-      <c r="A823" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A823" t="n">
+        <v>1823</v>
       </c>
       <c r="B823" t="inlineStr">
         <is>
@@ -79945,7 +79941,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N823" s="2" t="n">
+      <c r="N823" s="1" t="n">
         <v>44782</v>
       </c>
       <c r="O823" t="inlineStr">
@@ -79986,10 +79982,8 @@
       </c>
     </row>
     <row r="824">
-      <c r="A824" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A824" t="n">
+        <v>1823</v>
       </c>
       <c r="B824" t="inlineStr">
         <is>
@@ -80041,7 +80035,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N824" s="2" t="n">
+      <c r="N824" s="1" t="n">
         <v>46233</v>
       </c>
       <c r="O824" t="inlineStr">
@@ -80082,10 +80076,8 @@
       </c>
     </row>
     <row r="825">
-      <c r="A825" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A825" t="n">
+        <v>1823</v>
       </c>
       <c r="B825" t="inlineStr">
         <is>
@@ -80137,7 +80129,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N825" s="2" t="n">
+      <c r="N825" s="1" t="n">
         <v>46233</v>
       </c>
       <c r="O825" t="inlineStr">
@@ -80178,10 +80170,8 @@
       </c>
     </row>
     <row r="826">
-      <c r="A826" t="inlineStr">
-        <is>
-          <t>2728</t>
-        </is>
+      <c r="A826" t="n">
+        <v>2728</v>
       </c>
       <c r="B826" t="inlineStr">
         <is>
@@ -80233,7 +80223,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N826" s="2" t="n">
+      <c r="N826" s="1" t="n">
         <v>46237</v>
       </c>
       <c r="O826" t="inlineStr">
@@ -80274,10 +80264,8 @@
       </c>
     </row>
     <row r="827">
-      <c r="A827" t="inlineStr">
-        <is>
-          <t>3115</t>
-        </is>
+      <c r="A827" t="n">
+        <v>3115</v>
       </c>
       <c r="B827" t="inlineStr">
         <is>
@@ -80329,7 +80317,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N827" s="2" t="n">
+      <c r="N827" s="1" t="n">
         <v>46240</v>
       </c>
       <c r="O827" t="inlineStr">
@@ -80370,10 +80358,8 @@
       </c>
     </row>
     <row r="828">
-      <c r="A828" t="inlineStr">
-        <is>
-          <t>4111</t>
-        </is>
+      <c r="A828" t="n">
+        <v>4111</v>
       </c>
       <c r="B828" t="inlineStr">
         <is>
@@ -80425,7 +80411,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N828" s="2" t="n">
+      <c r="N828" s="1" t="n">
         <v>45104</v>
       </c>
       <c r="O828" t="inlineStr">
@@ -80466,10 +80452,8 @@
       </c>
     </row>
     <row r="829">
-      <c r="A829" t="inlineStr">
-        <is>
-          <t>4721</t>
-        </is>
+      <c r="A829" t="n">
+        <v>4721</v>
       </c>
       <c r="B829" t="inlineStr">
         <is>
@@ -80523,7 +80507,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N829" s="2" t="n">
+      <c r="N829" s="1" t="n">
         <v>46020</v>
       </c>
       <c r="O829" t="inlineStr">
@@ -80558,6 +80542,486 @@
         </is>
       </c>
       <c r="V829" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PONTIFICIA BOLIVARIANA</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F830" t="n">
+        <v>119565</v>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN INTELIGENCIA ARTIFICIAL Y CIENCIA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I830" t="n">
+        <v>133</v>
+      </c>
+      <c r="J830" t="n">
+        <v>8</v>
+      </c>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L830" t="inlineStr"/>
+      <c r="M830" t="inlineStr">
+        <is>
+          <t>Bimensual</t>
+        </is>
+      </c>
+      <c r="N830" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O830" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P830" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q830" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R830" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S830" t="inlineStr"/>
+      <c r="T830" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U830" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V830" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PONTIFICIA BOLIVARIANA</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F831" t="n">
+        <v>119564</v>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN INTELIGENCIA ARTIFICIAL Y CIENCIA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I831" t="n">
+        <v>133</v>
+      </c>
+      <c r="J831" t="n">
+        <v>8</v>
+      </c>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L831" t="inlineStr"/>
+      <c r="M831" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N831" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O831" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P831" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q831" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R831" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S831" t="inlineStr"/>
+      <c r="T831" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U831" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V831" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2842</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REFORMADA - CUR -</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F832" t="n">
+        <v>119570</v>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>INGENIERIA BIOMEDICA</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I832" t="n">
+        <v>155</v>
+      </c>
+      <c r="J832" t="n">
+        <v>10</v>
+      </c>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L832" t="inlineStr"/>
+      <c r="M832" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N832" s="2" t="n">
+        <v>44705</v>
+      </c>
+      <c r="O832" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P832" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q832" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R832" t="inlineStr">
+        <is>
+          <t>Ingeniería biomédica y afines</t>
+        </is>
+      </c>
+      <c r="S832" t="inlineStr"/>
+      <c r="T832" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U832" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V832" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2842</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REFORMADA - CUR -</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F833" t="n">
+        <v>119572</v>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>INGENIERIA INFORMATICA</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I833" t="n">
+        <v>158</v>
+      </c>
+      <c r="J833" t="n">
+        <v>10</v>
+      </c>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L833" t="inlineStr"/>
+      <c r="M833" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N833" s="2" t="n">
+        <v>44656</v>
+      </c>
+      <c r="O833" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P833" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q833" t="inlineStr">
+        <is>
+          <t>Uso de computadores</t>
+        </is>
+      </c>
+      <c r="R833" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S833" t="inlineStr"/>
+      <c r="T833" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U833" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V833" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F834" t="n">
+        <v>119442</v>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>PROFESIONAL EN BIOTECNOLOGÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I834" t="n">
+        <v>133</v>
+      </c>
+      <c r="J834" t="n">
+        <v>8</v>
+      </c>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L834" t="inlineStr"/>
+      <c r="M834" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N834" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="O834" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P834" t="inlineStr">
+        <is>
+          <t>Ciencias biológicas y afines</t>
+        </is>
+      </c>
+      <c r="Q834" t="inlineStr">
+        <is>
+          <t>Bioquímica</t>
+        </is>
+      </c>
+      <c r="R834" t="inlineStr">
+        <is>
+          <t>Biología, microbiología y afines</t>
+        </is>
+      </c>
+      <c r="S834" t="inlineStr"/>
+      <c r="T834" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="U834" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="V834" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V834"/>
+  <dimension ref="A1:V842"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80548,10 +80548,8 @@
       </c>
     </row>
     <row r="830">
-      <c r="A830" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A830" t="n">
+        <v>1710</v>
       </c>
       <c r="B830" t="inlineStr">
         <is>
@@ -80603,7 +80601,7 @@
           <t>Bimensual</t>
         </is>
       </c>
-      <c r="N830" s="2" t="n">
+      <c r="N830" s="1" t="n">
         <v>46154</v>
       </c>
       <c r="O830" t="inlineStr">
@@ -80644,10 +80642,8 @@
       </c>
     </row>
     <row r="831">
-      <c r="A831" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A831" t="n">
+        <v>1710</v>
       </c>
       <c r="B831" t="inlineStr">
         <is>
@@ -80699,7 +80695,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N831" s="2" t="n">
+      <c r="N831" s="1" t="n">
         <v>46154</v>
       </c>
       <c r="O831" t="inlineStr">
@@ -80740,10 +80736,8 @@
       </c>
     </row>
     <row r="832">
-      <c r="A832" t="inlineStr">
-        <is>
-          <t>2842</t>
-        </is>
+      <c r="A832" t="n">
+        <v>2842</v>
       </c>
       <c r="B832" t="inlineStr">
         <is>
@@ -80795,7 +80789,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N832" s="2" t="n">
+      <c r="N832" s="1" t="n">
         <v>44705</v>
       </c>
       <c r="O832" t="inlineStr">
@@ -80836,10 +80830,8 @@
       </c>
     </row>
     <row r="833">
-      <c r="A833" t="inlineStr">
-        <is>
-          <t>2842</t>
-        </is>
+      <c r="A833" t="n">
+        <v>2842</v>
       </c>
       <c r="B833" t="inlineStr">
         <is>
@@ -80891,7 +80883,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N833" s="2" t="n">
+      <c r="N833" s="1" t="n">
         <v>44656</v>
       </c>
       <c r="O833" t="inlineStr">
@@ -80932,10 +80924,8 @@
       </c>
     </row>
     <row r="834">
-      <c r="A834" t="inlineStr">
-        <is>
-          <t>3204</t>
-        </is>
+      <c r="A834" t="n">
+        <v>3204</v>
       </c>
       <c r="B834" t="inlineStr">
         <is>
@@ -80987,7 +80977,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N834" s="2" t="n">
+      <c r="N834" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="O834" t="inlineStr">
@@ -81022,6 +81012,778 @@
         </is>
       </c>
       <c r="V834" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DEL AREA ANDINA</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F835" t="n">
+        <v>119578</v>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE AGRONEGOCIOS</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I835" t="n">
+        <v>142</v>
+      </c>
+      <c r="J835" t="n">
+        <v>8</v>
+      </c>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L835" t="inlineStr"/>
+      <c r="M835" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N835" s="2" t="n">
+        <v>46206</v>
+      </c>
+      <c r="O835" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P835" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q835" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R835" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S835" t="inlineStr"/>
+      <c r="T835" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U835" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V835" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2731</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA CATOLICA LUMEN GENTIUM - UNICATÓLICA - CALI</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F836" t="n">
+        <v>106813</v>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>MERCADEO</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I836" t="n">
+        <v>162</v>
+      </c>
+      <c r="J836" t="n">
+        <v>9</v>
+      </c>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L836" t="n">
+        <v>3613829</v>
+      </c>
+      <c r="M836" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N836" s="2" t="n">
+        <v>43171</v>
+      </c>
+      <c r="O836" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P836" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q836" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R836" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S836" t="inlineStr"/>
+      <c r="T836" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U836" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V836" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>UNIVERSITARIA AGUSTINIANA- UNIAGUSTINIANA</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F837" t="n">
+        <v>119585</v>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>PUBLICIDAD DIGITAL</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I837" t="n">
+        <v>136</v>
+      </c>
+      <c r="J837" t="n">
+        <v>8</v>
+      </c>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L837" t="inlineStr"/>
+      <c r="M837" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N837" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="O837" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P837" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a artes y humanidades</t>
+        </is>
+      </c>
+      <c r="Q837" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a artes y humanidades</t>
+        </is>
+      </c>
+      <c r="R837" t="inlineStr">
+        <is>
+          <t>Publicidad y afines</t>
+        </is>
+      </c>
+      <c r="S837" t="inlineStr"/>
+      <c r="T837" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U837" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V837" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>UNIVERSITARIA AGUSTINIANA- UNIAGUSTINIANA</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F838" t="n">
+        <v>119586</v>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>PUBLICIDAD DIGITAL</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I838" t="n">
+        <v>136</v>
+      </c>
+      <c r="J838" t="n">
+        <v>8</v>
+      </c>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L838" t="inlineStr"/>
+      <c r="M838" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N838" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="O838" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P838" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="Q838" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="R838" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S838" t="inlineStr"/>
+      <c r="T838" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U838" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V838" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA - ITM</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F839" t="n">
+        <v>119577</v>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>BIOLOGÍA</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I839" t="n">
+        <v>141</v>
+      </c>
+      <c r="J839" t="n">
+        <v>9</v>
+      </c>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L839" t="inlineStr"/>
+      <c r="M839" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N839" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="O839" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P839" t="inlineStr">
+        <is>
+          <t>Ciencias biológicas y afines</t>
+        </is>
+      </c>
+      <c r="Q839" t="inlineStr">
+        <is>
+          <t>Biología</t>
+        </is>
+      </c>
+      <c r="R839" t="inlineStr">
+        <is>
+          <t>Biología, microbiología y afines</t>
+        </is>
+      </c>
+      <c r="S839" t="inlineStr"/>
+      <c r="T839" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U839" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="V839" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>3713</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA PARA EL DESARROLLO HUMANO - UNINPAHU</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F840" t="n">
+        <v>119587</v>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>COMUNICACIÓN SOCIAL Y PERIODISMO</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I840" t="n">
+        <v>144</v>
+      </c>
+      <c r="J840" t="n">
+        <v>8</v>
+      </c>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L840" t="inlineStr"/>
+      <c r="M840" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N840" s="2" t="n">
+        <v>44384</v>
+      </c>
+      <c r="O840" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P840" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q840" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R840" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S840" t="inlineStr"/>
+      <c r="T840" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U840" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V840" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>5802</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ECCI</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F841" t="n">
+        <v>107938</v>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>INGENIERIA AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I841" t="n">
+        <v>170</v>
+      </c>
+      <c r="J841" t="n">
+        <v>10</v>
+      </c>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L841" t="n">
+        <v>4605294</v>
+      </c>
+      <c r="M841" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N841" s="2" t="n">
+        <v>43557</v>
+      </c>
+      <c r="O841" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P841" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q841" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R841" t="inlineStr">
+        <is>
+          <t>Ingeniería ambiental, sanitaria y afines</t>
+        </is>
+      </c>
+      <c r="S841" t="inlineStr"/>
+      <c r="T841" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U841" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V841" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>9943</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>Villavicencio</t>
+        </is>
+      </c>
+      <c r="F842" t="n">
+        <v>119597</v>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE EMPRESAS AGROPECUARIAS</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I842" t="n">
+        <v>134</v>
+      </c>
+      <c r="J842" t="n">
+        <v>8</v>
+      </c>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L842" t="inlineStr"/>
+      <c r="M842" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N842" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="O842" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P842" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q842" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R842" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S842" t="inlineStr"/>
+      <c r="T842" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U842" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V842" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
